--- a/college_backend/iiit_combined.xlsx
+++ b/college_backend/iiit_combined.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arnav\OneDrive\Desktop\Counsellor - Copy - Copy\college_backend\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arnav\OneDrive\Desktop\The counsellor project\new\Counsellor - Copy - Copy\college_backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6396DF-2DE7-452A-8200-2E44B79BAA82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4535A81E-B35F-4586-A572-13ED5B7EB6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -367,9 +367,6 @@
     <t>Indian institute of information technology, Raichur, Karnataka</t>
   </si>
   <si>
-    <t>Karnataka</t>
-  </si>
-  <si>
     <t>Indian Institute of Information Technology, Vadodara International Campus Diu (IIITVICD)</t>
   </si>
   <si>
@@ -380,6 +377,9 @@
   </si>
   <si>
     <t>Nirf_Weightage</t>
+  </si>
+  <si>
+    <t>Raichur</t>
   </si>
 </sst>
 </file>
@@ -400,12 +400,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -437,7 +443,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -777,10 +783,10 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
@@ -803,7 +809,7 @@
         <v>8044</v>
       </c>
       <c r="G2">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
@@ -841,7 +847,7 @@
         <v>11529</v>
       </c>
       <c r="G3">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
@@ -879,7 +885,7 @@
         <v>212</v>
       </c>
       <c r="G4">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
@@ -917,7 +923,7 @@
         <v>1365</v>
       </c>
       <c r="G5">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
@@ -955,7 +961,7 @@
         <v>2013</v>
       </c>
       <c r="G6">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H6" t="s">
         <v>14</v>
@@ -993,7 +999,7 @@
         <v>3625</v>
       </c>
       <c r="G7">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
@@ -1031,7 +1037,7 @@
         <v>6214</v>
       </c>
       <c r="G8">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H8" t="s">
         <v>14</v>
@@ -1069,7 +1075,7 @@
         <v>195</v>
       </c>
       <c r="G9">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
@@ -1107,7 +1113,7 @@
         <v>2195</v>
       </c>
       <c r="G10">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H10" t="s">
         <v>14</v>
@@ -1145,7 +1151,7 @@
         <v>3313</v>
       </c>
       <c r="G11">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -1183,7 +1189,7 @@
         <v>67</v>
       </c>
       <c r="G12">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
@@ -1221,7 +1227,7 @@
         <v>1343</v>
       </c>
       <c r="G13">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H13" t="s">
         <v>14</v>
@@ -1259,7 +1265,7 @@
         <v>1493</v>
       </c>
       <c r="G14">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H14" t="s">
         <v>14</v>
@@ -1297,7 +1303,7 @@
         <v>75</v>
       </c>
       <c r="G15">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H15" t="s">
         <v>14</v>
@@ -1335,7 +1341,7 @@
         <v>17195</v>
       </c>
       <c r="G16">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H16" t="s">
         <v>14</v>
@@ -1373,7 +1379,7 @@
         <v>25669</v>
       </c>
       <c r="G17">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H17" t="s">
         <v>14</v>
@@ -1411,7 +1417,7 @@
         <v>1334</v>
       </c>
       <c r="G18">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H18" t="s">
         <v>14</v>
@@ -1449,7 +1455,7 @@
         <v>2803</v>
       </c>
       <c r="G19">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H19" t="s">
         <v>14</v>
@@ -1487,7 +1493,7 @@
         <v>4312</v>
       </c>
       <c r="G20">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H20" t="s">
         <v>14</v>
@@ -1525,7 +1531,7 @@
         <v>6543</v>
       </c>
       <c r="G21">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H21" t="s">
         <v>14</v>
@@ -1563,7 +1569,7 @@
         <v>13502</v>
       </c>
       <c r="G22">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H22" t="s">
         <v>14</v>
@@ -1601,7 +1607,7 @@
         <v>973</v>
       </c>
       <c r="G23">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H23" t="s">
         <v>14</v>
@@ -1639,7 +1645,7 @@
         <v>5088</v>
       </c>
       <c r="G24">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H24" t="s">
         <v>14</v>
@@ -1677,7 +1683,7 @@
         <v>4852</v>
       </c>
       <c r="G25">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H25" t="s">
         <v>14</v>
@@ -1715,7 +1721,7 @@
         <v>1671</v>
       </c>
       <c r="G26">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H26" t="s">
         <v>14</v>
@@ -1753,7 +1759,7 @@
         <v>13577</v>
       </c>
       <c r="G27">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H27" t="s">
         <v>14</v>
@@ -1791,7 +1797,7 @@
         <v>22022</v>
       </c>
       <c r="G28">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H28" t="s">
         <v>14</v>
@@ -1829,7 +1835,7 @@
         <v>776</v>
       </c>
       <c r="G29">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H29" t="s">
         <v>14</v>
@@ -1867,7 +1873,7 @@
         <v>555</v>
       </c>
       <c r="G30">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H30" t="s">
         <v>14</v>
@@ -1905,7 +1911,7 @@
         <v>2370</v>
       </c>
       <c r="G31">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H31" t="s">
         <v>14</v>
@@ -1943,7 +1949,7 @@
         <v>3809</v>
       </c>
       <c r="G32">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H32" t="s">
         <v>14</v>
@@ -1981,7 +1987,7 @@
         <v>6241</v>
       </c>
       <c r="G33">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H33" t="s">
         <v>14</v>
@@ -2019,7 +2025,7 @@
         <v>10475</v>
       </c>
       <c r="G34">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H34" t="s">
         <v>14</v>
@@ -2057,7 +2063,7 @@
         <v>557</v>
       </c>
       <c r="G35">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H35" t="s">
         <v>14</v>
@@ -2095,7 +2101,7 @@
         <v>4293</v>
       </c>
       <c r="G36">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H36" t="s">
         <v>14</v>
@@ -2133,7 +2139,7 @@
         <v>5371</v>
       </c>
       <c r="G37">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H37" t="s">
         <v>14</v>
@@ -2171,7 +2177,7 @@
         <v>1981</v>
       </c>
       <c r="G38">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H38" t="s">
         <v>14</v>
@@ -2209,7 +2215,7 @@
         <v>2568</v>
       </c>
       <c r="G39">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H39" t="s">
         <v>14</v>
@@ -2247,7 +2253,7 @@
         <v>16856</v>
       </c>
       <c r="G40">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H40" t="s">
         <v>14</v>
@@ -2285,7 +2291,7 @@
         <v>24511</v>
       </c>
       <c r="G41">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H41" t="s">
         <v>14</v>
@@ -2323,7 +2329,7 @@
         <v>1098</v>
       </c>
       <c r="G42">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H42" t="s">
         <v>14</v>
@@ -2361,7 +2367,7 @@
         <v>2790</v>
       </c>
       <c r="G43">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H43" t="s">
         <v>14</v>
@@ -2399,7 +2405,7 @@
         <v>4010</v>
       </c>
       <c r="G44">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H44" t="s">
         <v>14</v>
@@ -2437,7 +2443,7 @@
         <v>219</v>
       </c>
       <c r="G45">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H45" t="s">
         <v>14</v>
@@ -2475,7 +2481,7 @@
         <v>7482</v>
       </c>
       <c r="G46">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H46" t="s">
         <v>14</v>
@@ -2513,7 +2519,7 @@
         <v>10838</v>
       </c>
       <c r="G47">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H47" t="s">
         <v>14</v>
@@ -2551,7 +2557,7 @@
         <v>746</v>
       </c>
       <c r="G48">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H48" t="s">
         <v>14</v>
@@ -2589,7 +2595,7 @@
         <v>4746</v>
       </c>
       <c r="G49">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H49" t="s">
         <v>14</v>
@@ -2627,7 +2633,7 @@
         <v>5701</v>
       </c>
       <c r="G50">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H50" t="s">
         <v>14</v>
@@ -2665,7 +2671,7 @@
         <v>2526</v>
       </c>
       <c r="G51">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H51" t="s">
         <v>14</v>
@@ -2703,7 +2709,7 @@
         <v>2793</v>
       </c>
       <c r="G52">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H52" t="s">
         <v>14</v>
@@ -2741,7 +2747,7 @@
         <v>11180</v>
       </c>
       <c r="G53">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H53" t="s">
         <v>14</v>
@@ -2779,7 +2785,7 @@
         <v>18094</v>
       </c>
       <c r="G54">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H54" t="s">
         <v>14</v>
@@ -2817,7 +2823,7 @@
         <v>719</v>
       </c>
       <c r="G55">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H55" t="s">
         <v>14</v>
@@ -2855,7 +2861,7 @@
         <v>1908</v>
       </c>
       <c r="G56">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H56" t="s">
         <v>14</v>
@@ -2893,7 +2899,7 @@
         <v>3232</v>
       </c>
       <c r="G57">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H57" t="s">
         <v>14</v>
@@ -2931,7 +2937,7 @@
         <v>4863</v>
       </c>
       <c r="G58">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H58" t="s">
         <v>14</v>
@@ -2969,7 +2975,7 @@
         <v>9429</v>
       </c>
       <c r="G59">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H59" t="s">
         <v>14</v>
@@ -3007,7 +3013,7 @@
         <v>3476</v>
       </c>
       <c r="G60">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H60" t="s">
         <v>14</v>
@@ -3045,7 +3051,7 @@
         <v>1494</v>
       </c>
       <c r="G61">
-        <v>118000</v>
+        <v>133750</v>
       </c>
       <c r="H61" t="s">
         <v>14</v>
@@ -3083,7 +3089,7 @@
         <v>27124</v>
       </c>
       <c r="G62">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H62" t="s">
         <v>32</v>
@@ -3121,7 +3127,7 @@
         <v>34478</v>
       </c>
       <c r="G63">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H63" t="s">
         <v>32</v>
@@ -3159,7 +3165,7 @@
         <v>2185</v>
       </c>
       <c r="G64">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H64" t="s">
         <v>32</v>
@@ -3197,7 +3203,7 @@
         <v>4855</v>
       </c>
       <c r="G65">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H65" t="s">
         <v>32</v>
@@ -3235,7 +3241,7 @@
         <v>6523</v>
       </c>
       <c r="G66">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H66" t="s">
         <v>32</v>
@@ -3273,7 +3279,7 @@
         <v>11440</v>
       </c>
       <c r="G67">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H67" t="s">
         <v>32</v>
@@ -3311,7 +3317,7 @@
         <v>15390</v>
       </c>
       <c r="G68">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H68" t="s">
         <v>32</v>
@@ -3349,7 +3355,7 @@
         <v>1715</v>
       </c>
       <c r="G69">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H69" t="s">
         <v>32</v>
@@ -3387,7 +3393,7 @@
         <v>7643</v>
       </c>
       <c r="G70">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H70" t="s">
         <v>32</v>
@@ -3425,7 +3431,7 @@
         <v>10142</v>
       </c>
       <c r="G71">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H71" t="s">
         <v>32</v>
@@ -3463,7 +3469,7 @@
         <v>3559</v>
       </c>
       <c r="G72">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H72" t="s">
         <v>32</v>
@@ -3501,7 +3507,7 @@
         <v>4802</v>
       </c>
       <c r="G73">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H73" t="s">
         <v>32</v>
@@ -3539,7 +3545,7 @@
         <v>24416</v>
       </c>
       <c r="G74">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H74" t="s">
         <v>32</v>
@@ -3577,7 +3583,7 @@
         <v>34423</v>
       </c>
       <c r="G75">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H75" t="s">
         <v>32</v>
@@ -3615,7 +3621,7 @@
         <v>1619</v>
       </c>
       <c r="G76">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H76" t="s">
         <v>32</v>
@@ -3653,7 +3659,7 @@
         <v>2035</v>
       </c>
       <c r="G77">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H77" t="s">
         <v>32</v>
@@ -3691,7 +3697,7 @@
         <v>4630</v>
       </c>
       <c r="G78">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H78" t="s">
         <v>32</v>
@@ -3729,7 +3735,7 @@
         <v>6604</v>
       </c>
       <c r="G79">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H79" t="s">
         <v>32</v>
@@ -3767,7 +3773,7 @@
         <v>229</v>
       </c>
       <c r="G80">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H80" t="s">
         <v>32</v>
@@ -3805,7 +3811,7 @@
         <v>10658</v>
       </c>
       <c r="G81">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H81" t="s">
         <v>32</v>
@@ -3843,7 +3849,7 @@
         <v>14625</v>
       </c>
       <c r="G82">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H82" t="s">
         <v>32</v>
@@ -3881,7 +3887,7 @@
         <v>1525</v>
       </c>
       <c r="G83">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H83" t="s">
         <v>32</v>
@@ -3919,7 +3925,7 @@
         <v>7363</v>
       </c>
       <c r="G84">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H84" t="s">
         <v>32</v>
@@ -3957,7 +3963,7 @@
         <v>8483</v>
       </c>
       <c r="G85">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H85" t="s">
         <v>32</v>
@@ -3995,7 +4001,7 @@
         <v>3475</v>
       </c>
       <c r="G86">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H86" t="s">
         <v>32</v>
@@ -4033,7 +4039,7 @@
         <v>3832</v>
       </c>
       <c r="G87">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H87" t="s">
         <v>32</v>
@@ -4071,7 +4077,7 @@
         <v>34167</v>
       </c>
       <c r="G88">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H88" t="s">
         <v>32</v>
@@ -4109,7 +4115,7 @@
         <v>36589</v>
       </c>
       <c r="G89">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H89" t="s">
         <v>32</v>
@@ -4147,7 +4153,7 @@
         <v>295</v>
       </c>
       <c r="G90">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H90" t="s">
         <v>32</v>
@@ -4185,7 +4191,7 @@
         <v>6098</v>
       </c>
       <c r="G91">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H91" t="s">
         <v>32</v>
@@ -4223,7 +4229,7 @@
         <v>6833</v>
       </c>
       <c r="G92">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H92" t="s">
         <v>32</v>
@@ -4261,7 +4267,7 @@
         <v>14779</v>
       </c>
       <c r="G93">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H93" t="s">
         <v>32</v>
@@ -4299,7 +4305,7 @@
         <v>18565</v>
       </c>
       <c r="G94">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H94" t="s">
         <v>32</v>
@@ -4337,7 +4343,7 @@
         <v>1891</v>
       </c>
       <c r="G95">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H95" t="s">
         <v>32</v>
@@ -4375,7 +4381,7 @@
         <v>8653</v>
       </c>
       <c r="G96">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H96" t="s">
         <v>32</v>
@@ -4413,7 +4419,7 @@
         <v>10738</v>
       </c>
       <c r="G97">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H97" t="s">
         <v>32</v>
@@ -4451,7 +4457,7 @@
         <v>3604</v>
       </c>
       <c r="G98">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H98" t="s">
         <v>32</v>
@@ -4489,7 +4495,7 @@
         <v>4075</v>
       </c>
       <c r="G99">
-        <v>150400</v>
+        <v>209000</v>
       </c>
       <c r="H99" t="s">
         <v>32</v>
@@ -4527,7 +4533,7 @@
         <v>20821</v>
       </c>
       <c r="G100">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H100" t="s">
         <v>36</v>
@@ -4565,7 +4571,7 @@
         <v>30584</v>
       </c>
       <c r="G101">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H101" t="s">
         <v>36</v>
@@ -4603,7 +4609,7 @@
         <v>1082</v>
       </c>
       <c r="G102">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H102" t="s">
         <v>36</v>
@@ -4641,7 +4647,7 @@
         <v>2453</v>
       </c>
       <c r="G103">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H103" t="s">
         <v>36</v>
@@ -4679,7 +4685,7 @@
         <v>3551</v>
       </c>
       <c r="G104">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H104" t="s">
         <v>36</v>
@@ -4717,7 +4723,7 @@
         <v>5385</v>
       </c>
       <c r="G105">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H105" t="s">
         <v>36</v>
@@ -4755,7 +4761,7 @@
         <v>8445</v>
       </c>
       <c r="G106">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H106" t="s">
         <v>36</v>
@@ -4793,7 +4799,7 @@
         <v>13481</v>
       </c>
       <c r="G107">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H107" t="s">
         <v>36</v>
@@ -4831,7 +4837,7 @@
         <v>1399</v>
       </c>
       <c r="G108">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H108" t="s">
         <v>36</v>
@@ -4869,7 +4875,7 @@
         <v>5209</v>
       </c>
       <c r="G109">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H109" t="s">
         <v>36</v>
@@ -4907,7 +4913,7 @@
         <v>6963</v>
       </c>
       <c r="G110">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H110" t="s">
         <v>36</v>
@@ -4945,7 +4951,7 @@
         <v>141</v>
       </c>
       <c r="G111">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H111" t="s">
         <v>36</v>
@@ -4983,7 +4989,7 @@
         <v>2701</v>
       </c>
       <c r="G112">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H112" t="s">
         <v>36</v>
@@ -5021,7 +5027,7 @@
         <v>3264</v>
       </c>
       <c r="G113">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H113" t="s">
         <v>36</v>
@@ -5059,7 +5065,7 @@
         <v>30437</v>
       </c>
       <c r="G114">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H114" t="s">
         <v>36</v>
@@ -5097,7 +5103,7 @@
         <v>38176</v>
       </c>
       <c r="G115">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H115" t="s">
         <v>36</v>
@@ -5135,7 +5141,7 @@
         <v>2723</v>
       </c>
       <c r="G116">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H116" t="s">
         <v>36</v>
@@ -5173,7 +5179,7 @@
         <v>5528</v>
       </c>
       <c r="G117">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H117" t="s">
         <v>36</v>
@@ -5211,7 +5217,7 @@
         <v>6177</v>
       </c>
       <c r="G118">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H118" t="s">
         <v>36</v>
@@ -5249,7 +5255,7 @@
         <v>13518</v>
       </c>
       <c r="G119">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H119" t="s">
         <v>36</v>
@@ -5287,7 +5293,7 @@
         <v>17942</v>
       </c>
       <c r="G120">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H120" t="s">
         <v>36</v>
@@ -5325,7 +5331,7 @@
         <v>7079</v>
       </c>
       <c r="G121">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H121" t="s">
         <v>36</v>
@@ -5363,7 +5369,7 @@
         <v>8445</v>
       </c>
       <c r="G122">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H122" t="s">
         <v>36</v>
@@ -5401,7 +5407,7 @@
         <v>3531</v>
       </c>
       <c r="G123">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H123" t="s">
         <v>36</v>
@@ -5439,7 +5445,7 @@
         <v>3982</v>
       </c>
       <c r="G124">
-        <v>168500</v>
+        <v>275000</v>
       </c>
       <c r="H124" t="s">
         <v>36</v>
@@ -5477,7 +5483,7 @@
         <v>39991</v>
       </c>
       <c r="G125">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H125" t="s">
         <v>39</v>
@@ -5515,7 +5521,7 @@
         <v>38130</v>
       </c>
       <c r="G126">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H126" t="s">
         <v>39</v>
@@ -5553,7 +5559,7 @@
         <v>1271</v>
       </c>
       <c r="G127">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H127" t="s">
         <v>39</v>
@@ -5591,7 +5597,7 @@
         <v>6978</v>
       </c>
       <c r="G128">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H128" t="s">
         <v>39</v>
@@ -5629,7 +5635,7 @@
         <v>7343</v>
       </c>
       <c r="G129">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H129" t="s">
         <v>39</v>
@@ -5667,7 +5673,7 @@
         <v>16367</v>
       </c>
       <c r="G130">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H130" t="s">
         <v>39</v>
@@ -5705,7 +5711,7 @@
         <v>18234</v>
       </c>
       <c r="G131">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H131" t="s">
         <v>39</v>
@@ -5743,7 +5749,7 @@
         <v>1432</v>
       </c>
       <c r="G132">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H132" t="s">
         <v>39</v>
@@ -5781,7 +5787,7 @@
         <v>9255</v>
       </c>
       <c r="G133">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H133" t="s">
         <v>39</v>
@@ -5819,7 +5825,7 @@
         <v>8992</v>
       </c>
       <c r="G134">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H134" t="s">
         <v>39</v>
@@ -5857,7 +5863,7 @@
         <v>263</v>
       </c>
       <c r="G135">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H135" t="s">
         <v>39</v>
@@ -5895,7 +5901,7 @@
         <v>4176</v>
       </c>
       <c r="G136">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H136" t="s">
         <v>39</v>
@@ -5933,7 +5939,7 @@
         <v>4314</v>
       </c>
       <c r="G137">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H137" t="s">
         <v>39</v>
@@ -5971,7 +5977,7 @@
         <v>43031</v>
       </c>
       <c r="G138">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H138" t="s">
         <v>39</v>
@@ -6009,7 +6015,7 @@
         <v>42026</v>
       </c>
       <c r="G139">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H139" t="s">
         <v>39</v>
@@ -6047,7 +6053,7 @@
         <v>3291</v>
       </c>
       <c r="G140">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H140" t="s">
         <v>39</v>
@@ -6085,7 +6091,7 @@
         <v>7241</v>
       </c>
       <c r="G141">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H141" t="s">
         <v>39</v>
@@ -6123,7 +6129,7 @@
         <v>7628</v>
       </c>
       <c r="G142">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H142" t="s">
         <v>39</v>
@@ -6161,7 +6167,7 @@
         <v>17077</v>
       </c>
       <c r="G143">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H143" t="s">
         <v>39</v>
@@ -6199,7 +6205,7 @@
         <v>15369</v>
       </c>
       <c r="G144">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H144" t="s">
         <v>39</v>
@@ -6237,7 +6243,7 @@
         <v>9708</v>
       </c>
       <c r="G145">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H145" t="s">
         <v>39</v>
@@ -6275,7 +6281,7 @@
         <v>10443</v>
       </c>
       <c r="G146">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H146" t="s">
         <v>39</v>
@@ -6313,7 +6319,7 @@
         <v>4901</v>
       </c>
       <c r="G147">
-        <v>174300</v>
+        <v>228760</v>
       </c>
       <c r="H147" t="s">
         <v>39</v>
@@ -6351,7 +6357,7 @@
         <v>28994</v>
       </c>
       <c r="G148">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H148" t="s">
         <v>41</v>
@@ -6389,7 +6395,7 @@
         <v>1922</v>
       </c>
       <c r="G149">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H149" t="s">
         <v>41</v>
@@ -6427,7 +6433,7 @@
         <v>5038</v>
       </c>
       <c r="G150">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H150" t="s">
         <v>41</v>
@@ -6465,7 +6471,7 @@
         <v>12954</v>
       </c>
       <c r="G151">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H151" t="s">
         <v>41</v>
@@ -6503,7 +6509,7 @@
         <v>1382</v>
       </c>
       <c r="G152">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H152" t="s">
         <v>41</v>
@@ -6541,7 +6547,7 @@
         <v>8043</v>
       </c>
       <c r="G153">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H153" t="s">
         <v>41</v>
@@ -6579,7 +6585,7 @@
         <v>4306</v>
       </c>
       <c r="G154">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H154" t="s">
         <v>41</v>
@@ -6617,7 +6623,7 @@
         <v>31601</v>
       </c>
       <c r="G155">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H155" t="s">
         <v>41</v>
@@ -6655,7 +6661,7 @@
         <v>2644</v>
       </c>
       <c r="G156">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H156" t="s">
         <v>41</v>
@@ -6693,7 +6699,7 @@
         <v>5264</v>
       </c>
       <c r="G157">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H157" t="s">
         <v>41</v>
@@ -6731,7 +6737,7 @@
         <v>14380</v>
       </c>
       <c r="G158">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H158" t="s">
         <v>41</v>
@@ -6769,7 +6775,7 @@
         <v>1279</v>
       </c>
       <c r="G159">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H159" t="s">
         <v>41</v>
@@ -6807,7 +6813,7 @@
         <v>9056</v>
       </c>
       <c r="G160">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H160" t="s">
         <v>41</v>
@@ -6845,7 +6851,7 @@
         <v>4443</v>
       </c>
       <c r="G161">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H161" t="s">
         <v>41</v>
@@ -6883,7 +6889,7 @@
         <v>32173</v>
       </c>
       <c r="G162">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H162" t="s">
         <v>41</v>
@@ -6921,7 +6927,7 @@
         <v>1547</v>
       </c>
       <c r="G163">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H163" t="s">
         <v>41</v>
@@ -6959,7 +6965,7 @@
         <v>5444</v>
       </c>
       <c r="G164">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H164" t="s">
         <v>41</v>
@@ -6997,7 +7003,7 @@
         <v>14394</v>
       </c>
       <c r="G165">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H165" t="s">
         <v>41</v>
@@ -7035,7 +7041,7 @@
         <v>8919</v>
       </c>
       <c r="G166">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H166" t="s">
         <v>41</v>
@@ -7073,7 +7079,7 @@
         <v>4544</v>
       </c>
       <c r="G167">
-        <v>150383</v>
+        <v>200696</v>
       </c>
       <c r="H167" t="s">
         <v>41</v>
@@ -7111,7 +7117,7 @@
         <v>28335</v>
       </c>
       <c r="G168">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H168" t="s">
         <v>45</v>
@@ -7149,7 +7155,7 @@
         <v>28910</v>
       </c>
       <c r="G169">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H169" t="s">
         <v>45</v>
@@ -7187,7 +7193,7 @@
         <v>1505</v>
       </c>
       <c r="G170">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H170" t="s">
         <v>45</v>
@@ -7225,7 +7231,7 @@
         <v>5056</v>
       </c>
       <c r="G171">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H171" t="s">
         <v>45</v>
@@ -7263,7 +7269,7 @@
         <v>5436</v>
       </c>
       <c r="G172">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H172" t="s">
         <v>45</v>
@@ -7301,7 +7307,7 @@
         <v>12090</v>
       </c>
       <c r="G173">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H173" t="s">
         <v>45</v>
@@ -7339,7 +7345,7 @@
         <v>966</v>
       </c>
       <c r="G174">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H174" t="s">
         <v>45</v>
@@ -7377,7 +7383,7 @@
         <v>6890</v>
       </c>
       <c r="G175">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H175" t="s">
         <v>45</v>
@@ -7415,7 +7421,7 @@
         <v>3981</v>
       </c>
       <c r="G176">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H176" t="s">
         <v>45</v>
@@ -7453,7 +7459,7 @@
         <v>31872</v>
       </c>
       <c r="G177">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H177" t="s">
         <v>45</v>
@@ -7491,7 +7497,7 @@
         <v>484</v>
       </c>
       <c r="G178">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H178" t="s">
         <v>45</v>
@@ -7529,7 +7535,7 @@
         <v>5586</v>
       </c>
       <c r="G179">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H179" t="s">
         <v>45</v>
@@ -7567,7 +7573,7 @@
         <v>13111</v>
       </c>
       <c r="G180">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H180" t="s">
         <v>45</v>
@@ -7605,7 +7611,7 @@
         <v>8712</v>
       </c>
       <c r="G181">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H181" t="s">
         <v>45</v>
@@ -7643,7 +7649,7 @@
         <v>4580</v>
       </c>
       <c r="G182">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H182" t="s">
         <v>45</v>
@@ -7681,7 +7687,7 @@
         <v>30485</v>
       </c>
       <c r="G183">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H183" t="s">
         <v>45</v>
@@ -7719,7 +7725,7 @@
         <v>5484</v>
       </c>
       <c r="G184">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H184" t="s">
         <v>45</v>
@@ -7757,7 +7763,7 @@
         <v>13073</v>
       </c>
       <c r="G185">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H185" t="s">
         <v>45</v>
@@ -7795,7 +7801,7 @@
         <v>7990</v>
       </c>
       <c r="G186">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H186" t="s">
         <v>45</v>
@@ -7833,7 +7839,7 @@
         <v>4605</v>
       </c>
       <c r="G187">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H187" t="s">
         <v>45</v>
@@ -7871,7 +7877,7 @@
         <v>37935</v>
       </c>
       <c r="G188">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H188" t="s">
         <v>45</v>
@@ -7909,7 +7915,7 @@
         <v>37389</v>
       </c>
       <c r="G189">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H189" t="s">
         <v>45</v>
@@ -7947,7 +7953,7 @@
         <v>3688</v>
       </c>
       <c r="G190">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H190" t="s">
         <v>45</v>
@@ -7985,7 +7991,7 @@
         <v>6728</v>
       </c>
       <c r="G191">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H191" t="s">
         <v>45</v>
@@ -8023,7 +8029,7 @@
         <v>16185</v>
       </c>
       <c r="G192">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H192" t="s">
         <v>45</v>
@@ -8061,7 +8067,7 @@
         <v>17889</v>
       </c>
       <c r="G193">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H193" t="s">
         <v>45</v>
@@ -8099,7 +8105,7 @@
         <v>9737</v>
       </c>
       <c r="G194">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H194" t="s">
         <v>45</v>
@@ -8137,7 +8143,7 @@
         <v>10873</v>
       </c>
       <c r="G195">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H195" t="s">
         <v>45</v>
@@ -8175,7 +8181,7 @@
         <v>4987</v>
       </c>
       <c r="G196">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H196" t="s">
         <v>45</v>
@@ -8213,7 +8219,7 @@
         <v>33023</v>
       </c>
       <c r="G197">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H197" t="s">
         <v>45</v>
@@ -8251,7 +8257,7 @@
         <v>30920</v>
       </c>
       <c r="G198">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H198" t="s">
         <v>45</v>
@@ -8289,7 +8295,7 @@
         <v>1717</v>
       </c>
       <c r="G199">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H199" t="s">
         <v>45</v>
@@ -8327,7 +8333,7 @@
         <v>6044</v>
       </c>
       <c r="G200">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H200" t="s">
         <v>45</v>
@@ -8365,7 +8371,7 @@
         <v>14170</v>
       </c>
       <c r="G201">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H201" t="s">
         <v>45</v>
@@ -8403,7 +8409,7 @@
         <v>17018</v>
       </c>
       <c r="G202">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H202" t="s">
         <v>45</v>
@@ -8441,7 +8447,7 @@
         <v>9195</v>
       </c>
       <c r="G203">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H203" t="s">
         <v>45</v>
@@ -8479,7 +8485,7 @@
         <v>4937</v>
       </c>
       <c r="G204">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H204" t="s">
         <v>45</v>
@@ -8517,7 +8523,7 @@
         <v>4365</v>
       </c>
       <c r="G205">
-        <v>173190</v>
+        <v>260000</v>
       </c>
       <c r="H205" t="s">
         <v>45</v>
@@ -8555,7 +8561,7 @@
         <v>28509</v>
       </c>
       <c r="G206">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H206" t="s">
         <v>50</v>
@@ -8593,7 +8599,7 @@
         <v>32036</v>
       </c>
       <c r="G207">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H207" t="s">
         <v>50</v>
@@ -8631,7 +8637,7 @@
         <v>710</v>
       </c>
       <c r="G208">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H208" t="s">
         <v>50</v>
@@ -8669,7 +8675,7 @@
         <v>4983</v>
       </c>
       <c r="G209">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H209" t="s">
         <v>50</v>
@@ -8707,7 +8713,7 @@
         <v>11996</v>
       </c>
       <c r="G210">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H210" t="s">
         <v>50</v>
@@ -8745,7 +8751,7 @@
         <v>12461</v>
       </c>
       <c r="G211">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H211" t="s">
         <v>50</v>
@@ -8783,7 +8789,7 @@
         <v>7771</v>
       </c>
       <c r="G212">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H212" t="s">
         <v>50</v>
@@ -8821,7 +8827,7 @@
         <v>3902</v>
       </c>
       <c r="G213">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H213" t="s">
         <v>50</v>
@@ -8859,7 +8865,7 @@
         <v>26444</v>
       </c>
       <c r="G214">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H214" t="s">
         <v>50</v>
@@ -8897,7 +8903,7 @@
         <v>30676</v>
       </c>
       <c r="G215">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H215" t="s">
         <v>50</v>
@@ -8935,7 +8941,7 @@
         <v>1335</v>
       </c>
       <c r="G216">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H216" t="s">
         <v>50</v>
@@ -8973,7 +8979,7 @@
         <v>4857</v>
       </c>
       <c r="G217">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H217" t="s">
         <v>50</v>
@@ -9011,7 +9017,7 @@
         <v>5599</v>
       </c>
       <c r="G218">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H218" t="s">
         <v>50</v>
@@ -9049,7 +9055,7 @@
         <v>295</v>
       </c>
       <c r="G219">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H219" t="s">
         <v>50</v>
@@ -9087,7 +9093,7 @@
         <v>11112</v>
       </c>
       <c r="G220">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H220" t="s">
         <v>50</v>
@@ -9125,7 +9131,7 @@
         <v>12540</v>
       </c>
       <c r="G221">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H221" t="s">
         <v>50</v>
@@ -9163,7 +9169,7 @@
         <v>882</v>
       </c>
       <c r="G222">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H222" t="s">
         <v>50</v>
@@ -9201,7 +9207,7 @@
         <v>8121</v>
       </c>
       <c r="G223">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H223" t="s">
         <v>50</v>
@@ -9239,7 +9245,7 @@
         <v>7928</v>
       </c>
       <c r="G224">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H224" t="s">
         <v>50</v>
@@ -9277,7 +9283,7 @@
         <v>184</v>
       </c>
       <c r="G225">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H225" t="s">
         <v>50</v>
@@ -9315,7 +9321,7 @@
         <v>3930</v>
       </c>
       <c r="G226">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H226" t="s">
         <v>50</v>
@@ -9353,7 +9359,7 @@
         <v>2895</v>
       </c>
       <c r="G227">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H227" t="s">
         <v>50</v>
@@ -9391,7 +9397,7 @@
         <v>36490</v>
       </c>
       <c r="G228">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H228" t="s">
         <v>50</v>
@@ -9429,7 +9435,7 @@
         <v>38333</v>
       </c>
       <c r="G229">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H229" t="s">
         <v>50</v>
@@ -9467,7 +9473,7 @@
         <v>1774</v>
       </c>
       <c r="G230">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H230" t="s">
         <v>50</v>
@@ -9505,7 +9511,7 @@
         <v>6535</v>
       </c>
       <c r="G231">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H231" t="s">
         <v>50</v>
@@ -9543,7 +9549,7 @@
         <v>14065</v>
       </c>
       <c r="G232">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H232" t="s">
         <v>50</v>
@@ -9581,7 +9587,7 @@
         <v>13601</v>
       </c>
       <c r="G233">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H233" t="s">
         <v>50</v>
@@ -9619,7 +9625,7 @@
         <v>1333</v>
       </c>
       <c r="G234">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H234" t="s">
         <v>50</v>
@@ -9657,7 +9663,7 @@
         <v>9656</v>
       </c>
       <c r="G235">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H235" t="s">
         <v>50</v>
@@ -9695,7 +9701,7 @@
         <v>10281</v>
       </c>
       <c r="G236">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H236" t="s">
         <v>50</v>
@@ -9733,7 +9739,7 @@
         <v>4141</v>
       </c>
       <c r="G237">
-        <v>208300</v>
+        <v>332600</v>
       </c>
       <c r="H237" t="s">
         <v>50</v>
@@ -9771,7 +9777,7 @@
         <v>21838</v>
       </c>
       <c r="G238">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H238" t="s">
         <v>52</v>
@@ -9809,7 +9815,7 @@
         <v>30490</v>
       </c>
       <c r="G239">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H239" t="s">
         <v>52</v>
@@ -9847,7 +9853,7 @@
         <v>1946</v>
       </c>
       <c r="G240">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H240" t="s">
         <v>52</v>
@@ -9885,7 +9891,7 @@
         <v>681</v>
       </c>
       <c r="G241">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H241" t="s">
         <v>52</v>
@@ -9923,7 +9929,7 @@
         <v>4092</v>
       </c>
       <c r="G242">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H242" t="s">
         <v>52</v>
@@ -9961,7 +9967,7 @@
         <v>6025</v>
       </c>
       <c r="G243">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H243" t="s">
         <v>52</v>
@@ -9999,7 +10005,7 @@
         <v>390</v>
       </c>
       <c r="G244">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H244" t="s">
         <v>52</v>
@@ -10037,7 +10043,7 @@
         <v>9909</v>
       </c>
       <c r="G245">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H245" t="s">
         <v>52</v>
@@ -10075,7 +10081,7 @@
         <v>15791</v>
       </c>
       <c r="G246">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H246" t="s">
         <v>52</v>
@@ -10113,7 +10119,7 @@
         <v>1205</v>
       </c>
       <c r="G247">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H247" t="s">
         <v>52</v>
@@ -10151,7 +10157,7 @@
         <v>7532</v>
       </c>
       <c r="G248">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H248" t="s">
         <v>52</v>
@@ -10189,7 +10195,7 @@
         <v>7556</v>
       </c>
       <c r="G249">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H249" t="s">
         <v>52</v>
@@ -10227,7 +10233,7 @@
         <v>3451</v>
       </c>
       <c r="G250">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H250" t="s">
         <v>52</v>
@@ -10265,7 +10271,7 @@
         <v>2926</v>
       </c>
       <c r="G251">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H251" t="s">
         <v>52</v>
@@ -10303,7 +10309,7 @@
         <v>23624</v>
       </c>
       <c r="G252">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H252" t="s">
         <v>52</v>
@@ -10341,7 +10347,7 @@
         <v>33467</v>
       </c>
       <c r="G253">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H253" t="s">
         <v>52</v>
@@ -10379,7 +10385,7 @@
         <v>2100</v>
       </c>
       <c r="G254">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H254" t="s">
         <v>52</v>
@@ -10417,7 +10423,7 @@
         <v>4255</v>
       </c>
       <c r="G255">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H255" t="s">
         <v>52</v>
@@ -10455,7 +10461,7 @@
         <v>6420</v>
       </c>
       <c r="G256">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H256" t="s">
         <v>52</v>
@@ -10493,7 +10499,7 @@
         <v>11316</v>
       </c>
       <c r="G257">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H257" t="s">
         <v>52</v>
@@ -10531,7 +10537,7 @@
         <v>16080</v>
       </c>
       <c r="G258">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H258" t="s">
         <v>52</v>
@@ -10569,7 +10575,7 @@
         <v>8179</v>
       </c>
       <c r="G259">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H259" t="s">
         <v>52</v>
@@ -10607,7 +10613,7 @@
         <v>6596</v>
       </c>
       <c r="G260">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H260" t="s">
         <v>52</v>
@@ -10645,7 +10651,7 @@
         <v>3507</v>
       </c>
       <c r="G261">
-        <v>163810</v>
+        <v>240870</v>
       </c>
       <c r="H261" t="s">
         <v>52</v>
@@ -10683,7 +10689,7 @@
         <v>7758</v>
       </c>
       <c r="G262">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H262" t="s">
         <v>54</v>
@@ -10721,7 +10727,7 @@
         <v>14319</v>
       </c>
       <c r="G263">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H263" t="s">
         <v>54</v>
@@ -10759,7 +10765,7 @@
         <v>344</v>
       </c>
       <c r="G264">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H264" t="s">
         <v>54</v>
@@ -10797,7 +10803,7 @@
         <v>487</v>
       </c>
       <c r="G265">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H265" t="s">
         <v>54</v>
@@ -10835,7 +10841,7 @@
         <v>1376</v>
       </c>
       <c r="G266">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H266" t="s">
         <v>54</v>
@@ -10873,7 +10879,7 @@
         <v>2348</v>
       </c>
       <c r="G267">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H267" t="s">
         <v>54</v>
@@ -10911,7 +10917,7 @@
         <v>92</v>
       </c>
       <c r="G268">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H268" t="s">
         <v>54</v>
@@ -10949,7 +10955,7 @@
         <v>3558</v>
       </c>
       <c r="G269">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H269" t="s">
         <v>54</v>
@@ -10987,7 +10993,7 @@
         <v>7281</v>
       </c>
       <c r="G270">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H270" t="s">
         <v>54</v>
@@ -11025,7 +11031,7 @@
         <v>193</v>
       </c>
       <c r="G271">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H271" t="s">
         <v>54</v>
@@ -11063,7 +11069,7 @@
         <v>2402</v>
       </c>
       <c r="G272">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H272" t="s">
         <v>54</v>
@@ -11101,7 +11107,7 @@
         <v>4416</v>
       </c>
       <c r="G273">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H273" t="s">
         <v>54</v>
@@ -11139,7 +11145,7 @@
         <v>88</v>
       </c>
       <c r="G274">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H274" t="s">
         <v>54</v>
@@ -11177,7 +11183,7 @@
         <v>1310</v>
       </c>
       <c r="G275">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H275" t="s">
         <v>54</v>
@@ -11215,7 +11221,7 @@
         <v>2784</v>
       </c>
       <c r="G276">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H276" t="s">
         <v>54</v>
@@ -11253,7 +11259,7 @@
         <v>5202</v>
       </c>
       <c r="G277">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H277" t="s">
         <v>54</v>
@@ -11291,7 +11297,7 @@
         <v>9457</v>
       </c>
       <c r="G278">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H278" t="s">
         <v>54</v>
@@ -11329,7 +11335,7 @@
         <v>284</v>
       </c>
       <c r="G279">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H279" t="s">
         <v>54</v>
@@ -11367,7 +11373,7 @@
         <v>1011</v>
       </c>
       <c r="G280">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H280" t="s">
         <v>54</v>
@@ -11405,7 +11411,7 @@
         <v>986</v>
       </c>
       <c r="G281">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H281" t="s">
         <v>54</v>
@@ -11443,7 +11449,7 @@
         <v>1801</v>
       </c>
       <c r="G282">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H282" t="s">
         <v>54</v>
@@ -11481,7 +11487,7 @@
         <v>52</v>
       </c>
       <c r="G283">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H283" t="s">
         <v>54</v>
@@ -11519,7 +11525,7 @@
         <v>2509</v>
       </c>
       <c r="G284">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H284" t="s">
         <v>54</v>
@@ -11557,7 +11563,7 @@
         <v>5104</v>
       </c>
       <c r="G285">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H285" t="s">
         <v>54</v>
@@ -11595,7 +11601,7 @@
         <v>261</v>
       </c>
       <c r="G286">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H286" t="s">
         <v>54</v>
@@ -11633,7 +11639,7 @@
         <v>502</v>
       </c>
       <c r="G287">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H287" t="s">
         <v>54</v>
@@ -11671,7 +11677,7 @@
         <v>1562</v>
       </c>
       <c r="G288">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H288" t="s">
         <v>54</v>
@@ -11709,7 +11715,7 @@
         <v>3003</v>
       </c>
       <c r="G289">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H289" t="s">
         <v>54</v>
@@ -11747,7 +11753,7 @@
         <v>44</v>
       </c>
       <c r="G290">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H290" t="s">
         <v>54</v>
@@ -11785,7 +11791,7 @@
         <v>888</v>
       </c>
       <c r="G291">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H291" t="s">
         <v>54</v>
@@ -11823,7 +11829,7 @@
         <v>1879</v>
       </c>
       <c r="G292">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H292" t="s">
         <v>54</v>
@@ -11861,7 +11867,7 @@
         <v>5392</v>
       </c>
       <c r="G293">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H293" t="s">
         <v>54</v>
@@ -11899,7 +11905,7 @@
         <v>9754</v>
       </c>
       <c r="G294">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H294" t="s">
         <v>54</v>
@@ -11937,7 +11943,7 @@
         <v>280</v>
       </c>
       <c r="G295">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H295" t="s">
         <v>54</v>
@@ -11975,7 +11981,7 @@
         <v>994</v>
       </c>
       <c r="G296">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H296" t="s">
         <v>54</v>
@@ -12013,7 +12019,7 @@
         <v>2009</v>
       </c>
       <c r="G297">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H297" t="s">
         <v>54</v>
@@ -12051,7 +12057,7 @@
         <v>2639</v>
       </c>
       <c r="G298">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H298" t="s">
         <v>54</v>
@@ -12089,7 +12095,7 @@
         <v>5423</v>
       </c>
       <c r="G299">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H299" t="s">
         <v>54</v>
@@ -12127,7 +12133,7 @@
         <v>278</v>
       </c>
       <c r="G300">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H300" t="s">
         <v>54</v>
@@ -12165,7 +12171,7 @@
         <v>1695</v>
       </c>
       <c r="G301">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H301" t="s">
         <v>54</v>
@@ -12203,7 +12209,7 @@
         <v>836</v>
       </c>
       <c r="G302">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H302" t="s">
         <v>54</v>
@@ -12241,7 +12247,7 @@
         <v>952</v>
       </c>
       <c r="G303">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H303" t="s">
         <v>54</v>
@@ -12279,7 +12285,7 @@
         <v>1893</v>
       </c>
       <c r="G304">
-        <v>126725</v>
+        <v>179090</v>
       </c>
       <c r="H304" t="s">
         <v>54</v>
@@ -12317,7 +12323,7 @@
         <v>39290</v>
       </c>
       <c r="G305">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H305" t="s">
         <v>58</v>
@@ -12355,7 +12361,7 @@
         <v>7490</v>
       </c>
       <c r="G306">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H306" t="s">
         <v>58</v>
@@ -12393,7 +12399,7 @@
         <v>15798</v>
       </c>
       <c r="G307">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H307" t="s">
         <v>58</v>
@@ -12431,7 +12437,7 @@
         <v>1244</v>
       </c>
       <c r="G308">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H308" t="s">
         <v>58</v>
@@ -12469,7 +12475,7 @@
         <v>8025</v>
       </c>
       <c r="G309">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H309" t="s">
         <v>58</v>
@@ -12507,7 +12513,7 @@
         <v>3122</v>
       </c>
       <c r="G310">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H310" t="s">
         <v>58</v>
@@ -12545,7 +12551,7 @@
         <v>32117</v>
       </c>
       <c r="G311">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H311" t="s">
         <v>58</v>
@@ -12583,7 +12589,7 @@
         <v>40124</v>
       </c>
       <c r="G312">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H312" t="s">
         <v>58</v>
@@ -12621,7 +12627,7 @@
         <v>2109</v>
       </c>
       <c r="G313">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H313" t="s">
         <v>58</v>
@@ -12659,7 +12665,7 @@
         <v>5662</v>
       </c>
       <c r="G314">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H314" t="s">
         <v>58</v>
@@ -12697,7 +12703,7 @@
         <v>11387</v>
       </c>
       <c r="G315">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H315" t="s">
         <v>58</v>
@@ -12735,7 +12741,7 @@
         <v>14391</v>
       </c>
       <c r="G316">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H316" t="s">
         <v>58</v>
@@ -12773,7 +12779,7 @@
         <v>6619</v>
       </c>
       <c r="G317">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H317" t="s">
         <v>58</v>
@@ -12811,7 +12817,7 @@
         <v>8319</v>
       </c>
       <c r="G318">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H318" t="s">
         <v>58</v>
@@ -12849,7 +12855,7 @@
         <v>2960</v>
       </c>
       <c r="G319">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H319" t="s">
         <v>58</v>
@@ -12887,7 +12893,7 @@
         <v>27848</v>
       </c>
       <c r="G320">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H320" t="s">
         <v>58</v>
@@ -12925,7 +12931,7 @@
         <v>33349</v>
       </c>
       <c r="G321">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H321" t="s">
         <v>58</v>
@@ -12963,7 +12969,7 @@
         <v>2146</v>
       </c>
       <c r="G322">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H322" t="s">
         <v>58</v>
@@ -13001,7 +13007,7 @@
         <v>6451</v>
       </c>
       <c r="G323">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H323" t="s">
         <v>58</v>
@@ -13039,7 +13045,7 @@
         <v>6754</v>
       </c>
       <c r="G324">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H324" t="s">
         <v>58</v>
@@ -13077,7 +13083,7 @@
         <v>11284</v>
       </c>
       <c r="G325">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H325" t="s">
         <v>58</v>
@@ -13115,7 +13121,7 @@
         <v>10683</v>
       </c>
       <c r="G326">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H326" t="s">
         <v>58</v>
@@ -13153,7 +13159,7 @@
         <v>6008</v>
       </c>
       <c r="G327">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H327" t="s">
         <v>58</v>
@@ -13191,7 +13197,7 @@
         <v>2651</v>
       </c>
       <c r="G328">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H328" t="s">
         <v>58</v>
@@ -13229,7 +13235,7 @@
         <v>3518</v>
       </c>
       <c r="G329">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H329" t="s">
         <v>58</v>
@@ -13267,7 +13273,7 @@
         <v>18654</v>
       </c>
       <c r="G330">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H330" t="s">
         <v>58</v>
@@ -13305,7 +13311,7 @@
         <v>19604</v>
       </c>
       <c r="G331">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H331" t="s">
         <v>58</v>
@@ -13343,7 +13349,7 @@
         <v>655</v>
       </c>
       <c r="G332">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H332" t="s">
         <v>58</v>
@@ -13381,7 +13387,7 @@
         <v>571</v>
       </c>
       <c r="G333">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H333" t="s">
         <v>58</v>
@@ -13419,7 +13425,7 @@
         <v>3058</v>
       </c>
       <c r="G334">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H334" t="s">
         <v>58</v>
@@ -13457,7 +13463,7 @@
         <v>3215</v>
       </c>
       <c r="G335">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H335" t="s">
         <v>58</v>
@@ -13495,7 +13501,7 @@
         <v>173</v>
       </c>
       <c r="G336">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H336" t="s">
         <v>58</v>
@@ -13533,7 +13539,7 @@
         <v>7575</v>
       </c>
       <c r="G337">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H337" t="s">
         <v>58</v>
@@ -13571,7 +13577,7 @@
         <v>9420</v>
       </c>
       <c r="G338">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H338" t="s">
         <v>58</v>
@@ -13609,7 +13615,7 @@
         <v>265</v>
       </c>
       <c r="G339">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H339" t="s">
         <v>58</v>
@@ -13647,7 +13653,7 @@
         <v>4366</v>
       </c>
       <c r="G340">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H340" t="s">
         <v>58</v>
@@ -13685,7 +13691,7 @@
         <v>5547</v>
       </c>
       <c r="G341">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H341" t="s">
         <v>58</v>
@@ -13723,7 +13729,7 @@
         <v>2146</v>
       </c>
       <c r="G342">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H342" t="s">
         <v>58</v>
@@ -13761,7 +13767,7 @@
         <v>1976</v>
       </c>
       <c r="G343">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H343" t="s">
         <v>58</v>
@@ -13799,7 +13805,7 @@
         <v>22849</v>
       </c>
       <c r="G344">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H344" t="s">
         <v>58</v>
@@ -13837,7 +13843,7 @@
         <v>26500</v>
       </c>
       <c r="G345">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H345" t="s">
         <v>58</v>
@@ -13875,7 +13881,7 @@
         <v>866</v>
       </c>
       <c r="G346">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H346" t="s">
         <v>58</v>
@@ -13913,7 +13919,7 @@
         <v>4185</v>
       </c>
       <c r="G347">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H347" t="s">
         <v>58</v>
@@ -13951,7 +13957,7 @@
         <v>5384</v>
       </c>
       <c r="G348">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H348" t="s">
         <v>58</v>
@@ -13989,7 +13995,7 @@
         <v>8562</v>
       </c>
       <c r="G349">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H349" t="s">
         <v>58</v>
@@ -14027,7 +14033,7 @@
         <v>13194</v>
       </c>
       <c r="G350">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H350" t="s">
         <v>58</v>
@@ -14065,7 +14071,7 @@
         <v>594</v>
       </c>
       <c r="G351">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H351" t="s">
         <v>58</v>
@@ -14103,7 +14109,7 @@
         <v>5281</v>
       </c>
       <c r="G352">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H352" t="s">
         <v>58</v>
@@ -14141,7 +14147,7 @@
         <v>6597</v>
       </c>
       <c r="G353">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H353" t="s">
         <v>58</v>
@@ -14179,7 +14185,7 @@
         <v>302</v>
       </c>
       <c r="G354">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H354" t="s">
         <v>58</v>
@@ -14217,7 +14223,7 @@
         <v>2375</v>
       </c>
       <c r="G355">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H355" t="s">
         <v>58</v>
@@ -14255,7 +14261,7 @@
         <v>2683</v>
       </c>
       <c r="G356">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H356" t="s">
         <v>58</v>
@@ -14293,7 +14299,7 @@
         <v>18702</v>
       </c>
       <c r="G357">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H357" t="s">
         <v>58</v>
@@ -14331,7 +14337,7 @@
         <v>22163</v>
       </c>
       <c r="G358">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H358" t="s">
         <v>58</v>
@@ -14369,7 +14375,7 @@
         <v>436</v>
       </c>
       <c r="G359">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H359" t="s">
         <v>58</v>
@@ -14407,7 +14413,7 @@
         <v>3188</v>
       </c>
       <c r="G360">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H360" t="s">
         <v>58</v>
@@ -14445,7 +14451,7 @@
         <v>3765</v>
       </c>
       <c r="G361">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H361" t="s">
         <v>58</v>
@@ -14483,7 +14489,7 @@
         <v>7850</v>
       </c>
       <c r="G362">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H362" t="s">
         <v>58</v>
@@ -14521,7 +14527,7 @@
         <v>11166</v>
       </c>
       <c r="G363">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H363" t="s">
         <v>58</v>
@@ -14559,7 +14565,7 @@
         <v>385</v>
       </c>
       <c r="G364">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H364" t="s">
         <v>58</v>
@@ -14597,7 +14603,7 @@
         <v>4700</v>
       </c>
       <c r="G365">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H365" t="s">
         <v>58</v>
@@ -14635,7 +14641,7 @@
         <v>5862</v>
       </c>
       <c r="G366">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H366" t="s">
         <v>58</v>
@@ -14673,7 +14679,7 @@
         <v>2148</v>
       </c>
       <c r="G367">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H367" t="s">
         <v>58</v>
@@ -14711,7 +14717,7 @@
         <v>2009</v>
       </c>
       <c r="G368">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H368" t="s">
         <v>58</v>
@@ -14749,7 +14755,7 @@
         <v>27634</v>
       </c>
       <c r="G369">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H369" t="s">
         <v>58</v>
@@ -14787,7 +14793,7 @@
         <v>27644</v>
       </c>
       <c r="G370">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H370" t="s">
         <v>58</v>
@@ -14825,7 +14831,7 @@
         <v>1007</v>
       </c>
       <c r="G371">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H371" t="s">
         <v>58</v>
@@ -14863,7 +14869,7 @@
         <v>654</v>
       </c>
       <c r="G372">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H372" t="s">
         <v>58</v>
@@ -14901,7 +14907,7 @@
         <v>5126</v>
       </c>
       <c r="G373">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H373" t="s">
         <v>58</v>
@@ -14939,7 +14945,7 @@
         <v>5652</v>
       </c>
       <c r="G374">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H374" t="s">
         <v>58</v>
@@ -14977,7 +14983,7 @@
         <v>186</v>
       </c>
       <c r="G375">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H375" t="s">
         <v>58</v>
@@ -15015,7 +15021,7 @@
         <v>10157</v>
       </c>
       <c r="G376">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H376" t="s">
         <v>58</v>
@@ -15053,7 +15059,7 @@
         <v>13591</v>
       </c>
       <c r="G377">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H377" t="s">
         <v>58</v>
@@ -15091,7 +15097,7 @@
         <v>615</v>
       </c>
       <c r="G378">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H378" t="s">
         <v>58</v>
@@ -15129,7 +15135,7 @@
         <v>6140</v>
       </c>
       <c r="G379">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H379" t="s">
         <v>58</v>
@@ -15167,7 +15173,7 @@
         <v>6911</v>
       </c>
       <c r="G380">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H380" t="s">
         <v>58</v>
@@ -15205,7 +15211,7 @@
         <v>2609</v>
       </c>
       <c r="G381">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H381" t="s">
         <v>58</v>
@@ -15243,7 +15249,7 @@
         <v>2575</v>
       </c>
       <c r="G382">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H382" t="s">
         <v>58</v>
@@ -15281,7 +15287,7 @@
         <v>43513</v>
       </c>
       <c r="G383">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H383" t="s">
         <v>58</v>
@@ -15319,7 +15325,7 @@
         <v>47534</v>
       </c>
       <c r="G384">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H384" t="s">
         <v>58</v>
@@ -15357,7 +15363,7 @@
         <v>2030</v>
       </c>
       <c r="G385">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H385" t="s">
         <v>58</v>
@@ -15395,7 +15401,7 @@
         <v>2249</v>
       </c>
       <c r="G386">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H386" t="s">
         <v>58</v>
@@ -15433,7 +15439,7 @@
         <v>7902</v>
       </c>
       <c r="G387">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H387" t="s">
         <v>58</v>
@@ -15471,7 +15477,7 @@
         <v>9672</v>
       </c>
       <c r="G388">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H388" t="s">
         <v>58</v>
@@ -15509,7 +15515,7 @@
         <v>16443</v>
       </c>
       <c r="G389">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H389" t="s">
         <v>58</v>
@@ -15547,7 +15553,7 @@
         <v>19279</v>
       </c>
       <c r="G390">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H390" t="s">
         <v>58</v>
@@ -15585,7 +15591,7 @@
         <v>1186</v>
       </c>
       <c r="G391">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H391" t="s">
         <v>58</v>
@@ -15623,7 +15629,7 @@
         <v>8018</v>
       </c>
       <c r="G392">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H392" t="s">
         <v>58</v>
@@ -15661,7 +15667,7 @@
         <v>10505</v>
       </c>
       <c r="G393">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H393" t="s">
         <v>58</v>
@@ -15699,7 +15705,7 @@
         <v>3320</v>
       </c>
       <c r="G394">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H394" t="s">
         <v>58</v>
@@ -15737,7 +15743,7 @@
         <v>3247</v>
       </c>
       <c r="G395">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H395" t="s">
         <v>58</v>
@@ -15775,7 +15781,7 @@
         <v>48128</v>
       </c>
       <c r="G396">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H396" t="s">
         <v>58</v>
@@ -15813,7 +15819,7 @@
         <v>56354</v>
       </c>
       <c r="G397">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H397" t="s">
         <v>58</v>
@@ -15851,7 +15857,7 @@
         <v>1828</v>
       </c>
       <c r="G398">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H398" t="s">
         <v>58</v>
@@ -15889,7 +15895,7 @@
         <v>8656</v>
       </c>
       <c r="G399">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H399" t="s">
         <v>58</v>
@@ -15927,7 +15933,7 @@
         <v>10224</v>
       </c>
       <c r="G400">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H400" t="s">
         <v>58</v>
@@ -15965,7 +15971,7 @@
         <v>17165</v>
       </c>
       <c r="G401">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H401" t="s">
         <v>58</v>
@@ -16003,7 +16009,7 @@
         <v>19374</v>
       </c>
       <c r="G402">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H402" t="s">
         <v>58</v>
@@ -16041,7 +16047,7 @@
         <v>1173</v>
       </c>
       <c r="G403">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H403" t="s">
         <v>58</v>
@@ -16079,7 +16085,7 @@
         <v>9063</v>
       </c>
       <c r="G404">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H404" t="s">
         <v>58</v>
@@ -16117,7 +16123,7 @@
         <v>9853</v>
       </c>
       <c r="G405">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H405" t="s">
         <v>58</v>
@@ -16155,7 +16161,7 @@
         <v>3652</v>
       </c>
       <c r="G406">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H406" t="s">
         <v>58</v>
@@ -16193,7 +16199,7 @@
         <v>4853</v>
       </c>
       <c r="G407">
-        <v>124300</v>
+        <v>156050</v>
       </c>
       <c r="H407" t="s">
         <v>58</v>
@@ -16231,7 +16237,7 @@
         <v>14757</v>
       </c>
       <c r="G408">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H408" t="s">
         <v>66</v>
@@ -16269,7 +16275,7 @@
         <v>23022</v>
       </c>
       <c r="G409">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H409" t="s">
         <v>66</v>
@@ -16307,7 +16313,7 @@
         <v>974</v>
       </c>
       <c r="G410">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H410" t="s">
         <v>66</v>
@@ -16345,7 +16351,7 @@
         <v>1402</v>
       </c>
       <c r="G411">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H411" t="s">
         <v>66</v>
@@ -16383,7 +16389,7 @@
         <v>2443</v>
       </c>
       <c r="G412">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H412" t="s">
         <v>66</v>
@@ -16421,7 +16427,7 @@
         <v>4150</v>
       </c>
       <c r="G413">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H413" t="s">
         <v>66</v>
@@ -16459,7 +16465,7 @@
         <v>179</v>
       </c>
       <c r="G414">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H414" t="s">
         <v>66</v>
@@ -16497,7 +16503,7 @@
         <v>5785</v>
       </c>
       <c r="G415">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H415" t="s">
         <v>66</v>
@@ -16535,7 +16541,7 @@
         <v>9914</v>
       </c>
       <c r="G416">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H416" t="s">
         <v>66</v>
@@ -16573,7 +16579,7 @@
         <v>497</v>
       </c>
       <c r="G417">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H417" t="s">
         <v>66</v>
@@ -16611,7 +16617,7 @@
         <v>728</v>
       </c>
       <c r="G418">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H418" t="s">
         <v>66</v>
@@ -16649,7 +16655,7 @@
         <v>3905</v>
       </c>
       <c r="G419">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H419" t="s">
         <v>66</v>
@@ -16687,7 +16693,7 @@
         <v>5201</v>
       </c>
       <c r="G420">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H420" t="s">
         <v>66</v>
@@ -16725,7 +16731,7 @@
         <v>107</v>
       </c>
       <c r="G421">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H421" t="s">
         <v>66</v>
@@ -16763,7 +16769,7 @@
         <v>2003</v>
       </c>
       <c r="G422">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H422" t="s">
         <v>66</v>
@@ -16801,7 +16807,7 @@
         <v>2610</v>
       </c>
       <c r="G423">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H423" t="s">
         <v>66</v>
@@ -16839,7 +16845,7 @@
         <v>19106</v>
       </c>
       <c r="G424">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H424" t="s">
         <v>66</v>
@@ -16877,7 +16883,7 @@
         <v>27458</v>
       </c>
       <c r="G425">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H425" t="s">
         <v>66</v>
@@ -16915,7 +16921,7 @@
         <v>1279</v>
       </c>
       <c r="G426">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H426" t="s">
         <v>66</v>
@@ -16953,7 +16959,7 @@
         <v>1925</v>
       </c>
       <c r="G427">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H427" t="s">
         <v>66</v>
@@ -16991,7 +16997,7 @@
         <v>3231</v>
       </c>
       <c r="G428">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H428" t="s">
         <v>66</v>
@@ -17029,7 +17035,7 @@
         <v>4699</v>
       </c>
       <c r="G429">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H429" t="s">
         <v>66</v>
@@ -17067,7 +17073,7 @@
         <v>284</v>
       </c>
       <c r="G430">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H430" t="s">
         <v>66</v>
@@ -17105,7 +17111,7 @@
         <v>7514</v>
       </c>
       <c r="G431">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H431" t="s">
         <v>66</v>
@@ -17143,7 +17149,7 @@
         <v>12756</v>
       </c>
       <c r="G432">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H432" t="s">
         <v>66</v>
@@ -17181,7 +17187,7 @@
         <v>768</v>
       </c>
       <c r="G433">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H433" t="s">
         <v>66</v>
@@ -17219,7 +17225,7 @@
         <v>4945</v>
       </c>
       <c r="G434">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H434" t="s">
         <v>66</v>
@@ -17257,7 +17263,7 @@
         <v>7356</v>
       </c>
       <c r="G435">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H435" t="s">
         <v>66</v>
@@ -17295,7 +17301,7 @@
         <v>2464</v>
       </c>
       <c r="G436">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H436" t="s">
         <v>66</v>
@@ -17333,7 +17339,7 @@
         <v>3108</v>
       </c>
       <c r="G437">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H437" t="s">
         <v>66</v>
@@ -17371,7 +17377,7 @@
         <v>41353</v>
       </c>
       <c r="G438">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H438" t="s">
         <v>66</v>
@@ -17409,7 +17415,7 @@
         <v>50222</v>
       </c>
       <c r="G439">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H439" t="s">
         <v>66</v>
@@ -17447,7 +17453,7 @@
         <v>2412</v>
       </c>
       <c r="G440">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H440" t="s">
         <v>66</v>
@@ -17485,7 +17491,7 @@
         <v>7237</v>
       </c>
       <c r="G441">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H441" t="s">
         <v>66</v>
@@ -17523,7 +17529,7 @@
         <v>8257</v>
       </c>
       <c r="G442">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H442" t="s">
         <v>66</v>
@@ -17561,7 +17567,7 @@
         <v>16157</v>
       </c>
       <c r="G443">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H443" t="s">
         <v>66</v>
@@ -17599,7 +17605,7 @@
         <v>20662</v>
       </c>
       <c r="G444">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H444" t="s">
         <v>66</v>
@@ -17637,7 +17643,7 @@
         <v>7511</v>
       </c>
       <c r="G445">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H445" t="s">
         <v>66</v>
@@ -17675,7 +17681,7 @@
         <v>9237</v>
       </c>
       <c r="G446">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H446" t="s">
         <v>66</v>
@@ -17713,7 +17719,7 @@
         <v>2964</v>
       </c>
       <c r="G447">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H447" t="s">
         <v>66</v>
@@ -17751,7 +17757,7 @@
         <v>4155</v>
       </c>
       <c r="G448">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H448" t="s">
         <v>66</v>
@@ -17789,7 +17795,7 @@
         <v>49439</v>
       </c>
       <c r="G449">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H449" t="s">
         <v>66</v>
@@ -17827,7 +17833,7 @@
         <v>55789</v>
       </c>
       <c r="G450">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H450" t="s">
         <v>66</v>
@@ -17865,7 +17871,7 @@
         <v>3322</v>
       </c>
       <c r="G451">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H451" t="s">
         <v>66</v>
@@ -17903,7 +17909,7 @@
         <v>8414</v>
       </c>
       <c r="G452">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H452" t="s">
         <v>66</v>
@@ -17941,7 +17947,7 @@
         <v>10027</v>
       </c>
       <c r="G453">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H453" t="s">
         <v>66</v>
@@ -17979,7 +17985,7 @@
         <v>18176</v>
       </c>
       <c r="G454">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H454" t="s">
         <v>66</v>
@@ -18017,7 +18023,7 @@
         <v>22444</v>
       </c>
       <c r="G455">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H455" t="s">
         <v>66</v>
@@ -18055,7 +18061,7 @@
         <v>9556</v>
       </c>
       <c r="G456">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H456" t="s">
         <v>66</v>
@@ -18093,7 +18099,7 @@
         <v>11422</v>
       </c>
       <c r="G457">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H457" t="s">
         <v>66</v>
@@ -18131,7 +18137,7 @@
         <v>3818</v>
       </c>
       <c r="G458">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H458" t="s">
         <v>66</v>
@@ -18169,7 +18175,7 @@
         <v>4862</v>
       </c>
       <c r="G459">
-        <v>105250</v>
+        <v>180500</v>
       </c>
       <c r="H459" t="s">
         <v>66</v>
@@ -18207,7 +18213,7 @@
         <v>50509</v>
       </c>
       <c r="G460">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H460" t="s">
         <v>68</v>
@@ -18245,7 +18251,7 @@
         <v>52943</v>
       </c>
       <c r="G461">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H461" t="s">
         <v>68</v>
@@ -18283,7 +18289,7 @@
         <v>8512</v>
       </c>
       <c r="G462">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H462" t="s">
         <v>68</v>
@@ -18321,7 +18327,7 @@
         <v>9469</v>
       </c>
       <c r="G463">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H463" t="s">
         <v>68</v>
@@ -18359,7 +18365,7 @@
         <v>18624</v>
       </c>
       <c r="G464">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H464" t="s">
         <v>68</v>
@@ -18397,7 +18403,7 @@
         <v>21886</v>
       </c>
       <c r="G465">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H465" t="s">
         <v>68</v>
@@ -18435,7 +18441,7 @@
         <v>10707</v>
       </c>
       <c r="G466">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H466" t="s">
         <v>68</v>
@@ -18473,7 +18479,7 @@
         <v>11636</v>
       </c>
       <c r="G467">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H467" t="s">
         <v>68</v>
@@ -18511,7 +18517,7 @@
         <v>4697</v>
       </c>
       <c r="G468">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H468" t="s">
         <v>68</v>
@@ -18549,7 +18555,7 @@
         <v>5132</v>
       </c>
       <c r="G469">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H469" t="s">
         <v>68</v>
@@ -18587,7 +18593,7 @@
         <v>47179</v>
       </c>
       <c r="G470">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H470" t="s">
         <v>68</v>
@@ -18625,7 +18631,7 @@
         <v>8361</v>
       </c>
       <c r="G471">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H471" t="s">
         <v>68</v>
@@ -18663,7 +18669,7 @@
         <v>18235</v>
       </c>
       <c r="G472">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H472" t="s">
         <v>68</v>
@@ -18701,7 +18707,7 @@
         <v>10255</v>
       </c>
       <c r="G473">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H473" t="s">
         <v>68</v>
@@ -18739,7 +18745,7 @@
         <v>4768</v>
       </c>
       <c r="G474">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H474" t="s">
         <v>68</v>
@@ -18777,7 +18783,7 @@
         <v>55833</v>
       </c>
       <c r="G475">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H475" t="s">
         <v>68</v>
@@ -18815,7 +18821,7 @@
         <v>67091</v>
       </c>
       <c r="G476">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H476" t="s">
         <v>68</v>
@@ -18853,7 +18859,7 @@
         <v>9513</v>
       </c>
       <c r="G477">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H477" t="s">
         <v>68</v>
@@ -18891,7 +18897,7 @@
         <v>11091</v>
       </c>
       <c r="G478">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H478" t="s">
         <v>68</v>
@@ -18929,7 +18935,7 @@
         <v>19882</v>
       </c>
       <c r="G479">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H479" t="s">
         <v>68</v>
@@ -18967,7 +18973,7 @@
         <v>23856</v>
       </c>
       <c r="G480">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H480" t="s">
         <v>68</v>
@@ -19005,7 +19011,7 @@
         <v>11358</v>
       </c>
       <c r="G481">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H481" t="s">
         <v>68</v>
@@ -19043,7 +19049,7 @@
         <v>12681</v>
       </c>
       <c r="G482">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H482" t="s">
         <v>68</v>
@@ -19081,7 +19087,7 @@
         <v>5242</v>
       </c>
       <c r="G483">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H483" t="s">
         <v>68</v>
@@ -19119,7 +19125,7 @@
         <v>5504</v>
       </c>
       <c r="G484">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H484" t="s">
         <v>68</v>
@@ -19157,7 +19163,7 @@
         <v>56550</v>
       </c>
       <c r="G485">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H485" t="s">
         <v>68</v>
@@ -19195,7 +19201,7 @@
         <v>9658</v>
       </c>
       <c r="G486">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H486" t="s">
         <v>68</v>
@@ -19233,7 +19239,7 @@
         <v>20128</v>
       </c>
       <c r="G487">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H487" t="s">
         <v>68</v>
@@ -19271,7 +19277,7 @@
         <v>11176</v>
       </c>
       <c r="G488">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H488" t="s">
         <v>68</v>
@@ -19309,7 +19315,7 @@
         <v>5349</v>
       </c>
       <c r="G489">
-        <v>165150</v>
+        <v>230900</v>
       </c>
       <c r="H489" t="s">
         <v>68</v>
@@ -19347,7 +19353,7 @@
         <v>29303</v>
       </c>
       <c r="G490">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H490" t="s">
         <v>72</v>
@@ -19385,7 +19391,7 @@
         <v>32237</v>
       </c>
       <c r="G491">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H491" t="s">
         <v>72</v>
@@ -19423,7 +19429,7 @@
         <v>827</v>
       </c>
       <c r="G492">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H492" t="s">
         <v>72</v>
@@ -19461,7 +19467,7 @@
         <v>1710</v>
       </c>
       <c r="G493">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H493" t="s">
         <v>72</v>
@@ -19499,7 +19505,7 @@
         <v>5173</v>
       </c>
       <c r="G494">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H494" t="s">
         <v>72</v>
@@ -19537,7 +19543,7 @@
         <v>6443</v>
       </c>
       <c r="G495">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H495" t="s">
         <v>72</v>
@@ -19575,7 +19581,7 @@
         <v>11994</v>
       </c>
       <c r="G496">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H496" t="s">
         <v>72</v>
@@ -19613,7 +19619,7 @@
         <v>15906</v>
       </c>
       <c r="G497">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H497" t="s">
         <v>72</v>
@@ -19651,7 +19657,7 @@
         <v>5985</v>
       </c>
       <c r="G498">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H498" t="s">
         <v>72</v>
@@ -19689,7 +19695,7 @@
         <v>8427</v>
       </c>
       <c r="G499">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H499" t="s">
         <v>72</v>
@@ -19727,7 +19733,7 @@
         <v>2170</v>
       </c>
       <c r="G500">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H500" t="s">
         <v>72</v>
@@ -19765,7 +19771,7 @@
         <v>3293</v>
       </c>
       <c r="G501">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H501" t="s">
         <v>72</v>
@@ -19803,7 +19809,7 @@
         <v>36702</v>
       </c>
       <c r="G502">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H502" t="s">
         <v>72</v>
@@ -19841,7 +19847,7 @@
         <v>41732</v>
       </c>
       <c r="G503">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H503" t="s">
         <v>72</v>
@@ -19879,7 +19885,7 @@
         <v>1699</v>
       </c>
       <c r="G504">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H504" t="s">
         <v>72</v>
@@ -19917,7 +19923,7 @@
         <v>6710</v>
       </c>
       <c r="G505">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H505" t="s">
         <v>72</v>
@@ -19955,7 +19961,7 @@
         <v>7703</v>
       </c>
       <c r="G506">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H506" t="s">
         <v>72</v>
@@ -19993,7 +19999,7 @@
         <v>15120</v>
       </c>
       <c r="G507">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H507" t="s">
         <v>72</v>
@@ -20031,7 +20037,7 @@
         <v>17553</v>
       </c>
       <c r="G508">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H508" t="s">
         <v>72</v>
@@ -20069,7 +20075,7 @@
         <v>1104</v>
       </c>
       <c r="G509">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H509" t="s">
         <v>72</v>
@@ -20107,7 +20113,7 @@
         <v>1178</v>
       </c>
       <c r="G510">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H510" t="s">
         <v>72</v>
@@ -20145,7 +20151,7 @@
         <v>7890</v>
       </c>
       <c r="G511">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H511" t="s">
         <v>72</v>
@@ -20183,7 +20189,7 @@
         <v>9822</v>
       </c>
       <c r="G512">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H512" t="s">
         <v>72</v>
@@ -20221,7 +20227,7 @@
         <v>3408</v>
       </c>
       <c r="G513">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H513" t="s">
         <v>72</v>
@@ -20259,7 +20265,7 @@
         <v>3853</v>
       </c>
       <c r="G514">
-        <v>176400</v>
+        <v>147850</v>
       </c>
       <c r="H514" t="s">
         <v>72</v>
@@ -20297,7 +20303,7 @@
         <v>9824</v>
       </c>
       <c r="G515">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H515" t="s">
         <v>75</v>
@@ -20335,7 +20341,7 @@
         <v>13117</v>
       </c>
       <c r="G516">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H516" t="s">
         <v>75</v>
@@ -20373,7 +20379,7 @@
         <v>482</v>
       </c>
       <c r="G517">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H517" t="s">
         <v>75</v>
@@ -20411,7 +20417,7 @@
         <v>1639</v>
       </c>
       <c r="G518">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H518" t="s">
         <v>75</v>
@@ -20449,7 +20455,7 @@
         <v>4262</v>
       </c>
       <c r="G519">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H519" t="s">
         <v>75</v>
@@ -20487,7 +20493,7 @@
         <v>7118</v>
       </c>
       <c r="G520">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H520" t="s">
         <v>75</v>
@@ -20525,7 +20531,7 @@
         <v>403</v>
       </c>
       <c r="G521">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H521" t="s">
         <v>75</v>
@@ -20563,7 +20569,7 @@
         <v>3139</v>
       </c>
       <c r="G522">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H522" t="s">
         <v>75</v>
@@ -20601,7 +20607,7 @@
         <v>5463</v>
       </c>
       <c r="G523">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H523" t="s">
         <v>75</v>
@@ -20639,7 +20645,7 @@
         <v>1776</v>
       </c>
       <c r="G524">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H524" t="s">
         <v>75</v>
@@ -20677,7 +20683,7 @@
         <v>2783</v>
       </c>
       <c r="G525">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H525" t="s">
         <v>75</v>
@@ -20715,7 +20721,7 @@
         <v>9384</v>
       </c>
       <c r="G526">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H526" t="s">
         <v>75</v>
@@ -20753,7 +20759,7 @@
         <v>14286</v>
       </c>
       <c r="G527">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H527" t="s">
         <v>75</v>
@@ -20791,7 +20797,7 @@
         <v>230</v>
       </c>
       <c r="G528">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H528" t="s">
         <v>75</v>
@@ -20829,7 +20835,7 @@
         <v>1575</v>
       </c>
       <c r="G529">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H529" t="s">
         <v>75</v>
@@ -20867,7 +20873,7 @@
         <v>2265</v>
       </c>
       <c r="G530">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H530" t="s">
         <v>75</v>
@@ -20905,7 +20911,7 @@
         <v>4064</v>
       </c>
       <c r="G531">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H531" t="s">
         <v>75</v>
@@ -20943,7 +20949,7 @@
         <v>8046</v>
       </c>
       <c r="G532">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H532" t="s">
         <v>75</v>
@@ -20981,7 +20987,7 @@
         <v>264</v>
       </c>
       <c r="G533">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H533" t="s">
         <v>75</v>
@@ -21019,7 +21025,7 @@
         <v>3240</v>
       </c>
       <c r="G534">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H534" t="s">
         <v>75</v>
@@ -21057,7 +21063,7 @@
         <v>5200</v>
       </c>
       <c r="G535">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H535" t="s">
         <v>75</v>
@@ -21095,7 +21101,7 @@
         <v>170</v>
       </c>
       <c r="G536">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H536" t="s">
         <v>75</v>
@@ -21133,7 +21139,7 @@
         <v>1751</v>
       </c>
       <c r="G537">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H537" t="s">
         <v>75</v>
@@ -21171,7 +21177,7 @@
         <v>1822</v>
       </c>
       <c r="G538">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H538" t="s">
         <v>75</v>
@@ -21209,7 +21215,7 @@
         <v>11380</v>
       </c>
       <c r="G539">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H539" t="s">
         <v>75</v>
@@ -21247,7 +21253,7 @@
         <v>18827</v>
       </c>
       <c r="G540">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H540" t="s">
         <v>75</v>
@@ -21285,7 +21291,7 @@
         <v>528</v>
       </c>
       <c r="G541">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H541" t="s">
         <v>75</v>
@@ -21323,7 +21329,7 @@
         <v>1857</v>
       </c>
       <c r="G542">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H542" t="s">
         <v>75</v>
@@ -21361,7 +21367,7 @@
         <v>2928</v>
       </c>
       <c r="G543">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H543" t="s">
         <v>75</v>
@@ -21399,7 +21405,7 @@
         <v>4884</v>
       </c>
       <c r="G544">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H544" t="s">
         <v>75</v>
@@ -21437,7 +21443,7 @@
         <v>8268</v>
       </c>
       <c r="G545">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H545" t="s">
         <v>75</v>
@@ -21475,7 +21481,7 @@
         <v>437</v>
       </c>
       <c r="G546">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H546" t="s">
         <v>75</v>
@@ -21513,7 +21519,7 @@
         <v>1035</v>
       </c>
       <c r="G547">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H547" t="s">
         <v>75</v>
@@ -21551,7 +21557,7 @@
         <v>3888</v>
       </c>
       <c r="G548">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H548" t="s">
         <v>75</v>
@@ -21589,7 +21595,7 @@
         <v>6157</v>
       </c>
       <c r="G549">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H549" t="s">
         <v>75</v>
@@ -21627,7 +21633,7 @@
         <v>2255</v>
       </c>
       <c r="G550">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H550" t="s">
         <v>75</v>
@@ -21665,7 +21671,7 @@
         <v>3442</v>
       </c>
       <c r="G551">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H551" t="s">
         <v>75</v>
@@ -21703,7 +21709,7 @@
         <v>11494</v>
       </c>
       <c r="G552">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H552" t="s">
         <v>75</v>
@@ -21741,7 +21747,7 @@
         <v>18522</v>
       </c>
       <c r="G553">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H553" t="s">
         <v>75</v>
@@ -21779,7 +21785,7 @@
         <v>648</v>
       </c>
       <c r="G554">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H554" t="s">
         <v>75</v>
@@ -21817,7 +21823,7 @@
         <v>1927</v>
       </c>
       <c r="G555">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H555" t="s">
         <v>75</v>
@@ -21855,7 +21861,7 @@
         <v>2055</v>
       </c>
       <c r="G556">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H556" t="s">
         <v>75</v>
@@ -21893,7 +21899,7 @@
         <v>3019</v>
       </c>
       <c r="G557">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H557" t="s">
         <v>75</v>
@@ -21931,7 +21937,7 @@
         <v>4959</v>
       </c>
       <c r="G558">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H558" t="s">
         <v>75</v>
@@ -21969,7 +21975,7 @@
         <v>9152</v>
       </c>
       <c r="G559">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H559" t="s">
         <v>75</v>
@@ -22007,7 +22013,7 @@
         <v>630</v>
       </c>
       <c r="G560">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H560" t="s">
         <v>75</v>
@@ -22045,7 +22051,7 @@
         <v>4019</v>
       </c>
       <c r="G561">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H561" t="s">
         <v>75</v>
@@ -22083,7 +22089,7 @@
         <v>6111</v>
       </c>
       <c r="G562">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H562" t="s">
         <v>75</v>
@@ -22121,7 +22127,7 @@
         <v>2178</v>
       </c>
       <c r="G563">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H563" t="s">
         <v>75</v>
@@ -22159,7 +22165,7 @@
         <v>3716</v>
       </c>
       <c r="G564">
-        <v>149600</v>
+        <v>263200</v>
       </c>
       <c r="H564" t="s">
         <v>75</v>
@@ -22197,7 +22203,7 @@
         <v>37419</v>
       </c>
       <c r="G565">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H565" t="s">
         <v>79</v>
@@ -22235,7 +22241,7 @@
         <v>39855</v>
       </c>
       <c r="G566">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H566" t="s">
         <v>79</v>
@@ -22273,7 +22279,7 @@
         <v>1246</v>
       </c>
       <c r="G567">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H567" t="s">
         <v>79</v>
@@ -22311,7 +22317,7 @@
         <v>6763</v>
       </c>
       <c r="G568">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H568" t="s">
         <v>79</v>
@@ -22349,7 +22355,7 @@
         <v>7570</v>
       </c>
       <c r="G569">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H569" t="s">
         <v>79</v>
@@ -22387,7 +22393,7 @@
         <v>308</v>
       </c>
       <c r="G570">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H570" t="s">
         <v>79</v>
@@ -22425,7 +22431,7 @@
         <v>15972</v>
       </c>
       <c r="G571">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H571" t="s">
         <v>79</v>
@@ -22463,7 +22469,7 @@
         <v>17907</v>
       </c>
       <c r="G572">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H572" t="s">
         <v>79</v>
@@ -22501,7 +22507,7 @@
         <v>785</v>
       </c>
       <c r="G573">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H573" t="s">
         <v>79</v>
@@ -22539,7 +22545,7 @@
         <v>9390</v>
       </c>
       <c r="G574">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H574" t="s">
         <v>79</v>
@@ -22577,7 +22583,7 @@
         <v>9769</v>
       </c>
       <c r="G575">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H575" t="s">
         <v>79</v>
@@ -22615,7 +22621,7 @@
         <v>99</v>
       </c>
       <c r="G576">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H576" t="s">
         <v>79</v>
@@ -22653,7 +22659,7 @@
         <v>3974</v>
       </c>
       <c r="G577">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H577" t="s">
         <v>79</v>
@@ -22691,7 +22697,7 @@
         <v>2087</v>
       </c>
       <c r="G578">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H578" t="s">
         <v>79</v>
@@ -22729,7 +22735,7 @@
         <v>39077</v>
       </c>
       <c r="G579">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H579" t="s">
         <v>79</v>
@@ -22767,7 +22773,7 @@
         <v>41400</v>
       </c>
       <c r="G580">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H580" t="s">
         <v>79</v>
@@ -22805,7 +22811,7 @@
         <v>990</v>
       </c>
       <c r="G581">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H581" t="s">
         <v>79</v>
@@ -22843,7 +22849,7 @@
         <v>6996</v>
       </c>
       <c r="G582">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H582" t="s">
         <v>79</v>
@@ -22881,7 +22887,7 @@
         <v>7668</v>
       </c>
       <c r="G583">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H583" t="s">
         <v>79</v>
@@ -22919,7 +22925,7 @@
         <v>373</v>
       </c>
       <c r="G584">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H584" t="s">
         <v>79</v>
@@ -22957,7 +22963,7 @@
         <v>16643</v>
       </c>
       <c r="G585">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H585" t="s">
         <v>79</v>
@@ -22995,7 +23001,7 @@
         <v>18574</v>
       </c>
       <c r="G586">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H586" t="s">
         <v>79</v>
@@ -23033,7 +23039,7 @@
         <v>1135</v>
       </c>
       <c r="G587">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H587" t="s">
         <v>79</v>
@@ -23071,7 +23077,7 @@
         <v>9861</v>
       </c>
       <c r="G588">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H588" t="s">
         <v>79</v>
@@ -23109,7 +23115,7 @@
         <v>10212</v>
       </c>
       <c r="G589">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H589" t="s">
         <v>79</v>
@@ -23147,7 +23153,7 @@
         <v>4447</v>
       </c>
       <c r="G590">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H590" t="s">
         <v>79</v>
@@ -23185,7 +23191,7 @@
         <v>3514</v>
       </c>
       <c r="G591">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H591" t="s">
         <v>79</v>
@@ -23223,7 +23229,7 @@
         <v>41143</v>
       </c>
       <c r="G592">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H592" t="s">
         <v>79</v>
@@ -23261,7 +23267,7 @@
         <v>43215</v>
       </c>
       <c r="G593">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H593" t="s">
         <v>79</v>
@@ -23299,7 +23305,7 @@
         <v>1378</v>
       </c>
       <c r="G594">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H594" t="s">
         <v>79</v>
@@ -23337,7 +23343,7 @@
         <v>7224</v>
       </c>
       <c r="G595">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H595" t="s">
         <v>79</v>
@@ -23375,7 +23381,7 @@
         <v>7285</v>
       </c>
       <c r="G596">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H596" t="s">
         <v>79</v>
@@ -23413,7 +23419,7 @@
         <v>16841</v>
       </c>
       <c r="G597">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H597" t="s">
         <v>79</v>
@@ -23451,7 +23457,7 @@
         <v>18957</v>
       </c>
       <c r="G598">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H598" t="s">
         <v>79</v>
@@ -23489,7 +23495,7 @@
         <v>635</v>
       </c>
       <c r="G599">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H599" t="s">
         <v>79</v>
@@ -23527,7 +23533,7 @@
         <v>10252</v>
       </c>
       <c r="G600">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H600" t="s">
         <v>79</v>
@@ -23565,7 +23571,7 @@
         <v>10883</v>
       </c>
       <c r="G601">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H601" t="s">
         <v>79</v>
@@ -23603,7 +23609,7 @@
         <v>144</v>
       </c>
       <c r="G602">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H602" t="s">
         <v>79</v>
@@ -23641,7 +23647,7 @@
         <v>4685</v>
       </c>
       <c r="G603">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H603" t="s">
         <v>79</v>
@@ -23679,7 +23685,7 @@
         <v>3771</v>
       </c>
       <c r="G604">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H604" t="s">
         <v>79</v>
@@ -23717,7 +23723,7 @@
         <v>92</v>
       </c>
       <c r="G605">
-        <v>212400</v>
+        <v>233000</v>
       </c>
       <c r="H605" t="s">
         <v>79</v>
@@ -23755,7 +23761,7 @@
         <v>36999</v>
       </c>
       <c r="G606">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H606" t="s">
         <v>82</v>
@@ -23793,7 +23799,7 @@
         <v>38027</v>
       </c>
       <c r="G607">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H607" t="s">
         <v>82</v>
@@ -23831,7 +23837,7 @@
         <v>578</v>
       </c>
       <c r="G608">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H608" t="s">
         <v>82</v>
@@ -23869,7 +23875,7 @@
         <v>6561</v>
       </c>
       <c r="G609">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H609" t="s">
         <v>82</v>
@@ -23907,7 +23913,7 @@
         <v>6571</v>
       </c>
       <c r="G610">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H610" t="s">
         <v>82</v>
@@ -23945,7 +23951,7 @@
         <v>14516</v>
       </c>
       <c r="G611">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H611" t="s">
         <v>82</v>
@@ -23983,7 +23989,7 @@
         <v>13940</v>
       </c>
       <c r="G612">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H612" t="s">
         <v>82</v>
@@ -24021,7 +24027,7 @@
         <v>412</v>
       </c>
       <c r="G613">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H613" t="s">
         <v>82</v>
@@ -24059,7 +24065,7 @@
         <v>6190</v>
       </c>
       <c r="G614">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H614" t="s">
         <v>82</v>
@@ -24097,7 +24103,7 @@
         <v>6661</v>
       </c>
       <c r="G615">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H615" t="s">
         <v>82</v>
@@ -24135,7 +24141,7 @@
         <v>2934</v>
       </c>
       <c r="G616">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H616" t="s">
         <v>82</v>
@@ -24173,7 +24179,7 @@
         <v>3498</v>
       </c>
       <c r="G617">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H617" t="s">
         <v>82</v>
@@ -24211,7 +24217,7 @@
         <v>32761</v>
       </c>
       <c r="G618">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H618" t="s">
         <v>82</v>
@@ -24249,7 +24255,7 @@
         <v>33001</v>
       </c>
       <c r="G619">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H619" t="s">
         <v>82</v>
@@ -24287,7 +24293,7 @@
         <v>491</v>
       </c>
       <c r="G620">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H620" t="s">
         <v>82</v>
@@ -24325,7 +24331,7 @@
         <v>5862</v>
       </c>
       <c r="G621">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H621" t="s">
         <v>82</v>
@@ -24363,7 +24369,7 @@
         <v>5702</v>
       </c>
       <c r="G622">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H622" t="s">
         <v>82</v>
@@ -24401,7 +24407,7 @@
         <v>13128</v>
       </c>
       <c r="G623">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H623" t="s">
         <v>82</v>
@@ -24439,7 +24445,7 @@
         <v>12828</v>
       </c>
       <c r="G624">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H624" t="s">
         <v>82</v>
@@ -24477,7 +24483,7 @@
         <v>317</v>
       </c>
       <c r="G625">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H625" t="s">
         <v>82</v>
@@ -24515,7 +24521,7 @@
         <v>5596</v>
       </c>
       <c r="G626">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H626" t="s">
         <v>82</v>
@@ -24553,7 +24559,7 @@
         <v>5148</v>
       </c>
       <c r="G627">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H627" t="s">
         <v>82</v>
@@ -24591,7 +24597,7 @@
         <v>2305</v>
       </c>
       <c r="G628">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H628" t="s">
         <v>82</v>
@@ -24629,7 +24635,7 @@
         <v>2129</v>
       </c>
       <c r="G629">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H629" t="s">
         <v>82</v>
@@ -24667,7 +24673,7 @@
         <v>37958</v>
       </c>
       <c r="G630">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H630" t="s">
         <v>82</v>
@@ -24705,7 +24711,7 @@
         <v>6378</v>
       </c>
       <c r="G631">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H631" t="s">
         <v>82</v>
@@ -24743,7 +24749,7 @@
         <v>15367</v>
       </c>
       <c r="G632">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H632" t="s">
         <v>82</v>
@@ -24781,7 +24787,7 @@
         <v>546</v>
       </c>
       <c r="G633">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H633" t="s">
         <v>82</v>
@@ -24819,7 +24825,7 @@
         <v>6939</v>
       </c>
       <c r="G634">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H634" t="s">
         <v>82</v>
@@ -24857,7 +24863,7 @@
         <v>1814</v>
       </c>
       <c r="G635">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H635" t="s">
         <v>82</v>
@@ -24895,7 +24901,7 @@
         <v>42606</v>
       </c>
       <c r="G636">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H636" t="s">
         <v>82</v>
@@ -24933,7 +24939,7 @@
         <v>2076</v>
       </c>
       <c r="G637">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H637" t="s">
         <v>82</v>
@@ -24971,7 +24977,7 @@
         <v>7207</v>
       </c>
       <c r="G638">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H638" t="s">
         <v>82</v>
@@ -25009,7 +25015,7 @@
         <v>16891</v>
       </c>
       <c r="G639">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H639" t="s">
         <v>82</v>
@@ -25047,7 +25053,7 @@
         <v>7918</v>
       </c>
       <c r="G640">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H640" t="s">
         <v>82</v>
@@ -25085,7 +25091,7 @@
         <v>3398</v>
       </c>
       <c r="G641">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H641" t="s">
         <v>82</v>
@@ -25123,7 +25129,7 @@
         <v>41985</v>
       </c>
       <c r="G642">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H642" t="s">
         <v>82</v>
@@ -25161,7 +25167,7 @@
         <v>37555</v>
       </c>
       <c r="G643">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H643" t="s">
         <v>82</v>
@@ -25199,7 +25205,7 @@
         <v>926</v>
       </c>
       <c r="G644">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H644" t="s">
         <v>82</v>
@@ -25237,7 +25243,7 @@
         <v>7053</v>
       </c>
       <c r="G645">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H645" t="s">
         <v>82</v>
@@ -25275,7 +25281,7 @@
         <v>7043</v>
       </c>
       <c r="G646">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H646" t="s">
         <v>82</v>
@@ -25313,7 +25319,7 @@
         <v>16831</v>
       </c>
       <c r="G647">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H647" t="s">
         <v>82</v>
@@ -25351,7 +25357,7 @@
         <v>13679</v>
       </c>
       <c r="G648">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H648" t="s">
         <v>82</v>
@@ -25389,7 +25395,7 @@
         <v>7695</v>
       </c>
       <c r="G649">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H649" t="s">
         <v>82</v>
@@ -25427,7 +25433,7 @@
         <v>7776</v>
       </c>
       <c r="G650">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H650" t="s">
         <v>82</v>
@@ -25465,7 +25471,7 @@
         <v>3301</v>
       </c>
       <c r="G651">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H651" t="s">
         <v>82</v>
@@ -25503,7 +25509,7 @@
         <v>50444</v>
       </c>
       <c r="G652">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H652" t="s">
         <v>82</v>
@@ -25541,7 +25547,7 @@
         <v>8770</v>
       </c>
       <c r="G653">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H653" t="s">
         <v>82</v>
@@ -25579,7 +25585,7 @@
         <v>18228</v>
       </c>
       <c r="G654">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H654" t="s">
         <v>82</v>
@@ -25617,7 +25623,7 @@
         <v>9460</v>
       </c>
       <c r="G655">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H655" t="s">
         <v>82</v>
@@ -25655,7 +25661,7 @@
         <v>3824</v>
       </c>
       <c r="G656">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H656" t="s">
         <v>82</v>
@@ -25693,7 +25699,7 @@
         <v>49886</v>
       </c>
       <c r="G657">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H657" t="s">
         <v>82</v>
@@ -25731,7 +25737,7 @@
         <v>52652</v>
       </c>
       <c r="G658">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H658" t="s">
         <v>82</v>
@@ -25769,7 +25775,7 @@
         <v>2884</v>
       </c>
       <c r="G659">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H659" t="s">
         <v>82</v>
@@ -25807,7 +25813,7 @@
         <v>8530</v>
       </c>
       <c r="G660">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H660" t="s">
         <v>82</v>
@@ -25845,7 +25851,7 @@
         <v>18149</v>
       </c>
       <c r="G661">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H661" t="s">
         <v>82</v>
@@ -25883,7 +25889,7 @@
         <v>19787</v>
       </c>
       <c r="G662">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H662" t="s">
         <v>82</v>
@@ -25921,7 +25927,7 @@
         <v>1477</v>
       </c>
       <c r="G663">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H663" t="s">
         <v>82</v>
@@ -25959,7 +25965,7 @@
         <v>8903</v>
       </c>
       <c r="G664">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H664" t="s">
         <v>82</v>
@@ -25997,7 +26003,7 @@
         <v>10907</v>
       </c>
       <c r="G665">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H665" t="s">
         <v>82</v>
@@ -26035,7 +26041,7 @@
         <v>3817</v>
       </c>
       <c r="G666">
-        <v>122400</v>
+        <v>175800</v>
       </c>
       <c r="H666" t="s">
         <v>82</v>
@@ -26073,7 +26079,7 @@
         <v>35996</v>
       </c>
       <c r="G667">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H667" t="s">
         <v>88</v>
@@ -26111,7 +26117,7 @@
         <v>40151</v>
       </c>
       <c r="G668">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H668" t="s">
         <v>88</v>
@@ -26149,7 +26155,7 @@
         <v>2524</v>
       </c>
       <c r="G669">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H669" t="s">
         <v>88</v>
@@ -26187,7 +26193,7 @@
         <v>1475</v>
       </c>
       <c r="G670">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H670" t="s">
         <v>88</v>
@@ -26225,7 +26231,7 @@
         <v>6586</v>
       </c>
       <c r="G671">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H671" t="s">
         <v>88</v>
@@ -26263,7 +26269,7 @@
         <v>7599</v>
       </c>
       <c r="G672">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H672" t="s">
         <v>88</v>
@@ -26301,7 +26307,7 @@
         <v>378</v>
       </c>
       <c r="G673">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H673" t="s">
         <v>88</v>
@@ -26339,7 +26345,7 @@
         <v>14629</v>
       </c>
       <c r="G674">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H674" t="s">
         <v>88</v>
@@ -26377,7 +26383,7 @@
         <v>15875</v>
       </c>
       <c r="G675">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H675" t="s">
         <v>88</v>
@@ -26415,7 +26421,7 @@
         <v>1509</v>
       </c>
       <c r="G676">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H676" t="s">
         <v>88</v>
@@ -26453,7 +26459,7 @@
         <v>1136</v>
       </c>
       <c r="G677">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H677" t="s">
         <v>88</v>
@@ -26491,7 +26497,7 @@
         <v>9967</v>
       </c>
       <c r="G678">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H678" t="s">
         <v>88</v>
@@ -26529,7 +26535,7 @@
         <v>10470</v>
       </c>
       <c r="G679">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H679" t="s">
         <v>88</v>
@@ -26567,7 +26573,7 @@
         <v>4217</v>
       </c>
       <c r="G680">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H680" t="s">
         <v>88</v>
@@ -26605,7 +26611,7 @@
         <v>4454</v>
       </c>
       <c r="G681">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H681" t="s">
         <v>88</v>
@@ -26643,7 +26649,7 @@
         <v>32727</v>
       </c>
       <c r="G682">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H682" t="s">
         <v>88</v>
@@ -26681,7 +26687,7 @@
         <v>33437</v>
       </c>
       <c r="G683">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H683" t="s">
         <v>88</v>
@@ -26719,7 +26725,7 @@
         <v>961</v>
       </c>
       <c r="G684">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H684" t="s">
         <v>88</v>
@@ -26757,7 +26763,7 @@
         <v>5717</v>
       </c>
       <c r="G685">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H685" t="s">
         <v>88</v>
@@ -26795,7 +26801,7 @@
         <v>6782</v>
       </c>
       <c r="G686">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H686" t="s">
         <v>88</v>
@@ -26833,7 +26839,7 @@
         <v>12084</v>
       </c>
       <c r="G687">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H687" t="s">
         <v>88</v>
@@ -26871,7 +26877,7 @@
         <v>12777</v>
       </c>
       <c r="G688">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H688" t="s">
         <v>88</v>
@@ -26909,7 +26915,7 @@
         <v>488</v>
       </c>
       <c r="G689">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H689" t="s">
         <v>88</v>
@@ -26947,7 +26953,7 @@
         <v>8046</v>
       </c>
       <c r="G690">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H690" t="s">
         <v>88</v>
@@ -26985,7 +26991,7 @@
         <v>9891</v>
       </c>
       <c r="G691">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H691" t="s">
         <v>88</v>
@@ -27023,7 +27029,7 @@
         <v>3731</v>
       </c>
       <c r="G692">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H692" t="s">
         <v>88</v>
@@ -27061,7 +27067,7 @@
         <v>4576</v>
       </c>
       <c r="G693">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H693" t="s">
         <v>88</v>
@@ -27099,7 +27105,7 @@
         <v>36976</v>
       </c>
       <c r="G694">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H694" t="s">
         <v>88</v>
@@ -27137,7 +27143,7 @@
         <v>41306</v>
       </c>
       <c r="G695">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H695" t="s">
         <v>88</v>
@@ -27175,7 +27181,7 @@
         <v>1597</v>
       </c>
       <c r="G696">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H696" t="s">
         <v>88</v>
@@ -27213,7 +27219,7 @@
         <v>6670</v>
       </c>
       <c r="G697">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H697" t="s">
         <v>88</v>
@@ -27251,7 +27257,7 @@
         <v>7650</v>
       </c>
       <c r="G698">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H698" t="s">
         <v>88</v>
@@ -27289,7 +27295,7 @@
         <v>14983</v>
       </c>
       <c r="G699">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H699" t="s">
         <v>88</v>
@@ -27327,7 +27333,7 @@
         <v>15932</v>
       </c>
       <c r="G700">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H700" t="s">
         <v>88</v>
@@ -27365,7 +27371,7 @@
         <v>931</v>
       </c>
       <c r="G701">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H701" t="s">
         <v>88</v>
@@ -27403,7 +27409,7 @@
         <v>9327</v>
       </c>
       <c r="G702">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H702" t="s">
         <v>88</v>
@@ -27441,7 +27447,7 @@
         <v>10065</v>
       </c>
       <c r="G703">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H703" t="s">
         <v>88</v>
@@ -27479,7 +27485,7 @@
         <v>4219</v>
       </c>
       <c r="G704">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H704" t="s">
         <v>88</v>
@@ -27517,7 +27523,7 @@
         <v>4845</v>
       </c>
       <c r="G705">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H705" t="s">
         <v>88</v>
@@ -27555,7 +27561,7 @@
         <v>39875</v>
       </c>
       <c r="G706">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H706" t="s">
         <v>88</v>
@@ -27593,7 +27599,7 @@
         <v>40028</v>
       </c>
       <c r="G707">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H707" t="s">
         <v>88</v>
@@ -27631,7 +27637,7 @@
         <v>2395</v>
       </c>
       <c r="G708">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H708" t="s">
         <v>88</v>
@@ -27669,7 +27675,7 @@
         <v>6912</v>
       </c>
       <c r="G709">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H709" t="s">
         <v>88</v>
@@ -27707,7 +27713,7 @@
         <v>7621</v>
       </c>
       <c r="G710">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H710" t="s">
         <v>88</v>
@@ -27745,7 +27751,7 @@
         <v>15467</v>
       </c>
       <c r="G711">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H711" t="s">
         <v>88</v>
@@ -27783,7 +27789,7 @@
         <v>16560</v>
       </c>
       <c r="G712">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H712" t="s">
         <v>88</v>
@@ -27821,7 +27827,7 @@
         <v>1696</v>
       </c>
       <c r="G713">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H713" t="s">
         <v>88</v>
@@ -27859,7 +27865,7 @@
         <v>10131</v>
       </c>
       <c r="G714">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H714" t="s">
         <v>88</v>
@@ -27897,7 +27903,7 @@
         <v>10207</v>
       </c>
       <c r="G715">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H715" t="s">
         <v>88</v>
@@ -27935,7 +27941,7 @@
         <v>4152</v>
       </c>
       <c r="G716">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H716" t="s">
         <v>88</v>
@@ -27973,7 +27979,7 @@
         <v>4659</v>
       </c>
       <c r="G717">
-        <v>192875</v>
+        <v>395525</v>
       </c>
       <c r="H717" t="s">
         <v>88</v>
@@ -28011,7 +28017,7 @@
         <v>32429</v>
       </c>
       <c r="G718">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H718" t="s">
         <v>91</v>
@@ -28049,7 +28055,7 @@
         <v>1538</v>
       </c>
       <c r="G719">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H719" t="s">
         <v>91</v>
@@ -28087,7 +28093,7 @@
         <v>5894</v>
       </c>
       <c r="G720">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H720" t="s">
         <v>91</v>
@@ -28125,7 +28131,7 @@
         <v>255</v>
       </c>
       <c r="G721">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H721" t="s">
         <v>91</v>
@@ -28163,7 +28169,7 @@
         <v>13690</v>
       </c>
       <c r="G722">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H722" t="s">
         <v>91</v>
@@ -28201,7 +28207,7 @@
         <v>1588</v>
       </c>
       <c r="G723">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H723" t="s">
         <v>91</v>
@@ -28239,7 +28245,7 @@
         <v>8439</v>
       </c>
       <c r="G724">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H724" t="s">
         <v>91</v>
@@ -28277,7 +28283,7 @@
         <v>4172</v>
       </c>
       <c r="G725">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H725" t="s">
         <v>91</v>
@@ -28315,7 +28321,7 @@
         <v>31336</v>
       </c>
       <c r="G726">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H726" t="s">
         <v>91</v>
@@ -28353,7 +28359,7 @@
         <v>1514</v>
       </c>
       <c r="G727">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H727" t="s">
         <v>91</v>
@@ -28391,7 +28397,7 @@
         <v>5465</v>
       </c>
       <c r="G728">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H728" t="s">
         <v>91</v>
@@ -28429,7 +28435,7 @@
         <v>13354</v>
       </c>
       <c r="G729">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H729" t="s">
         <v>91</v>
@@ -28467,7 +28473,7 @@
         <v>8131</v>
       </c>
       <c r="G730">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H730" t="s">
         <v>91</v>
@@ -28505,7 +28511,7 @@
         <v>4382</v>
       </c>
       <c r="G731">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H731" t="s">
         <v>91</v>
@@ -28543,7 +28549,7 @@
         <v>40194</v>
       </c>
       <c r="G732">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H732" t="s">
         <v>91</v>
@@ -28581,7 +28587,7 @@
         <v>2651</v>
       </c>
       <c r="G733">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H733" t="s">
         <v>91</v>
@@ -28619,7 +28625,7 @@
         <v>7045</v>
       </c>
       <c r="G734">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H734" t="s">
         <v>91</v>
@@ -28657,7 +28663,7 @@
         <v>16809</v>
       </c>
       <c r="G735">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H735" t="s">
         <v>91</v>
@@ -28695,7 +28701,7 @@
         <v>1355</v>
       </c>
       <c r="G736">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H736" t="s">
         <v>91</v>
@@ -28733,7 +28739,7 @@
         <v>10111</v>
       </c>
       <c r="G737">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H737" t="s">
         <v>91</v>
@@ -28771,7 +28777,7 @@
         <v>4995</v>
       </c>
       <c r="G738">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H738" t="s">
         <v>91</v>
@@ -28809,7 +28815,7 @@
         <v>39295</v>
       </c>
       <c r="G739">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H739" t="s">
         <v>91</v>
@@ -28847,7 +28853,7 @@
         <v>3250</v>
       </c>
       <c r="G740">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H740" t="s">
         <v>91</v>
@@ -28885,7 +28891,7 @@
         <v>7047</v>
       </c>
       <c r="G741">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H741" t="s">
         <v>91</v>
@@ -28923,7 +28929,7 @@
         <v>16460</v>
       </c>
       <c r="G742">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H742" t="s">
         <v>91</v>
@@ -28961,7 +28967,7 @@
         <v>1662</v>
       </c>
       <c r="G743">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H743" t="s">
         <v>91</v>
@@ -28999,7 +29005,7 @@
         <v>9990</v>
       </c>
       <c r="G744">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H744" t="s">
         <v>91</v>
@@ -29037,7 +29043,7 @@
         <v>4691</v>
       </c>
       <c r="G745">
-        <v>161000</v>
+        <v>250000</v>
       </c>
       <c r="H745" t="s">
         <v>91</v>
@@ -29075,7 +29081,7 @@
         <v>27356</v>
       </c>
       <c r="G746">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H746" t="s">
         <v>95</v>
@@ -29113,7 +29119,7 @@
         <v>914</v>
       </c>
       <c r="G747">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H747" t="s">
         <v>95</v>
@@ -29151,7 +29157,7 @@
         <v>5189</v>
       </c>
       <c r="G748">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H748" t="s">
         <v>95</v>
@@ -29189,7 +29195,7 @@
         <v>165</v>
       </c>
       <c r="G749">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H749" t="s">
         <v>95</v>
@@ -29227,7 +29233,7 @@
         <v>11755</v>
       </c>
       <c r="G750">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H750" t="s">
         <v>95</v>
@@ -29265,7 +29271,7 @@
         <v>620</v>
       </c>
       <c r="G751">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H751" t="s">
         <v>95</v>
@@ -29303,7 +29309,7 @@
         <v>8228</v>
       </c>
       <c r="G752">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H752" t="s">
         <v>95</v>
@@ -29341,7 +29347,7 @@
         <v>211</v>
       </c>
       <c r="G753">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H753" t="s">
         <v>95</v>
@@ -29379,7 +29385,7 @@
         <v>3711</v>
       </c>
       <c r="G754">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H754" t="s">
         <v>95</v>
@@ -29417,7 +29423,7 @@
         <v>27105</v>
       </c>
       <c r="G755">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H755" t="s">
         <v>95</v>
@@ -29455,7 +29461,7 @@
         <v>986</v>
       </c>
       <c r="G756">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H756" t="s">
         <v>95</v>
@@ -29493,7 +29499,7 @@
         <v>4984</v>
       </c>
       <c r="G757">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H757" t="s">
         <v>95</v>
@@ -29531,7 +29537,7 @@
         <v>11474</v>
       </c>
       <c r="G758">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H758" t="s">
         <v>95</v>
@@ -29569,7 +29575,7 @@
         <v>510</v>
       </c>
       <c r="G759">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H759" t="s">
         <v>95</v>
@@ -29607,7 +29613,7 @@
         <v>7396</v>
       </c>
       <c r="G760">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H760" t="s">
         <v>95</v>
@@ -29645,7 +29651,7 @@
         <v>3381</v>
       </c>
       <c r="G761">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H761" t="s">
         <v>95</v>
@@ -29683,7 +29689,7 @@
         <v>28763</v>
       </c>
       <c r="G762">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H762" t="s">
         <v>95</v>
@@ -29721,7 +29727,7 @@
         <v>1008</v>
       </c>
       <c r="G763">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H763" t="s">
         <v>95</v>
@@ -29759,7 +29765,7 @@
         <v>5560</v>
       </c>
       <c r="G764">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H764" t="s">
         <v>95</v>
@@ -29797,7 +29803,7 @@
         <v>12500</v>
       </c>
       <c r="G765">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H765" t="s">
         <v>95</v>
@@ -29835,7 +29841,7 @@
         <v>741</v>
       </c>
       <c r="G766">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H766" t="s">
         <v>95</v>
@@ -29873,7 +29879,7 @@
         <v>8418</v>
       </c>
       <c r="G767">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H767" t="s">
         <v>95</v>
@@ -29911,7 +29917,7 @@
         <v>3395</v>
       </c>
       <c r="G768">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H768" t="s">
         <v>95</v>
@@ -29949,7 +29955,7 @@
         <v>30403</v>
       </c>
       <c r="G769">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H769" t="s">
         <v>95</v>
@@ -29987,7 +29993,7 @@
         <v>1070</v>
       </c>
       <c r="G770">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H770" t="s">
         <v>95</v>
@@ -30025,7 +30031,7 @@
         <v>5672</v>
       </c>
       <c r="G771">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H771" t="s">
         <v>95</v>
@@ -30063,7 +30069,7 @@
         <v>13132</v>
       </c>
       <c r="G772">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H772" t="s">
         <v>95</v>
@@ -30101,7 +30107,7 @@
         <v>987</v>
       </c>
       <c r="G773">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H773" t="s">
         <v>95</v>
@@ -30139,7 +30145,7 @@
         <v>8541</v>
       </c>
       <c r="G774">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H774" t="s">
         <v>95</v>
@@ -30177,7 +30183,7 @@
         <v>4174</v>
       </c>
       <c r="G775">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H775" t="s">
         <v>95</v>
@@ -30215,7 +30221,7 @@
         <v>37530</v>
       </c>
       <c r="G776">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H776" t="s">
         <v>95</v>
@@ -30253,7 +30259,7 @@
         <v>2341</v>
       </c>
       <c r="G777">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H777" t="s">
         <v>95</v>
@@ -30291,7 +30297,7 @@
         <v>6658</v>
       </c>
       <c r="G778">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H778" t="s">
         <v>95</v>
@@ -30329,7 +30335,7 @@
         <v>383</v>
       </c>
       <c r="G779">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H779" t="s">
         <v>95</v>
@@ -30367,7 +30373,7 @@
         <v>15792</v>
       </c>
       <c r="G780">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H780" t="s">
         <v>95</v>
@@ -30405,7 +30411,7 @@
         <v>1808</v>
       </c>
       <c r="G781">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H781" t="s">
         <v>95</v>
@@ -30443,7 +30449,7 @@
         <v>9718</v>
       </c>
       <c r="G782">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H782" t="s">
         <v>95</v>
@@ -30481,7 +30487,7 @@
         <v>4706</v>
       </c>
       <c r="G783">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H783" t="s">
         <v>95</v>
@@ -30519,7 +30525,7 @@
         <v>35608</v>
       </c>
       <c r="G784">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H784" t="s">
         <v>95</v>
@@ -30557,7 +30563,7 @@
         <v>1558</v>
       </c>
       <c r="G785">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H785" t="s">
         <v>95</v>
@@ -30595,7 +30601,7 @@
         <v>6585</v>
       </c>
       <c r="G786">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H786" t="s">
         <v>95</v>
@@ -30633,7 +30639,7 @@
         <v>15472</v>
       </c>
       <c r="G787">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H787" t="s">
         <v>95</v>
@@ -30671,7 +30677,7 @@
         <v>1607</v>
       </c>
       <c r="G788">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H788" t="s">
         <v>95</v>
@@ -30709,7 +30715,7 @@
         <v>9588</v>
       </c>
       <c r="G789">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H789" t="s">
         <v>95</v>
@@ -30747,7 +30753,7 @@
         <v>4628</v>
       </c>
       <c r="G790">
-        <v>168250</v>
+        <v>458000</v>
       </c>
       <c r="H790" t="s">
         <v>95</v>
@@ -30785,7 +30791,7 @@
         <v>18252</v>
       </c>
       <c r="G791">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H791" t="s">
         <v>101</v>
@@ -30823,7 +30829,7 @@
         <v>26196</v>
       </c>
       <c r="G792">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H792" t="s">
         <v>101</v>
@@ -30861,7 +30867,7 @@
         <v>856</v>
       </c>
       <c r="G793">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H793" t="s">
         <v>101</v>
@@ -30899,7 +30905,7 @@
         <v>396</v>
       </c>
       <c r="G794">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H794" t="s">
         <v>101</v>
@@ -30937,7 +30943,7 @@
         <v>3401</v>
       </c>
       <c r="G795">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H795" t="s">
         <v>101</v>
@@ -30975,7 +30981,7 @@
         <v>4864</v>
       </c>
       <c r="G796">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H796" t="s">
         <v>101</v>
@@ -31013,7 +31019,7 @@
         <v>247</v>
       </c>
       <c r="G797">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H797" t="s">
         <v>101</v>
@@ -31051,7 +31057,7 @@
         <v>8377</v>
       </c>
       <c r="G798">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H798" t="s">
         <v>101</v>
@@ -31089,7 +31095,7 @@
         <v>12521</v>
       </c>
       <c r="G799">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H799" t="s">
         <v>101</v>
@@ -31127,7 +31133,7 @@
         <v>775</v>
       </c>
       <c r="G800">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H800" t="s">
         <v>101</v>
@@ -31165,7 +31171,7 @@
         <v>454</v>
       </c>
       <c r="G801">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H801" t="s">
         <v>101</v>
@@ -31203,7 +31209,7 @@
         <v>5476</v>
       </c>
       <c r="G802">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H802" t="s">
         <v>101</v>
@@ -31241,7 +31247,7 @@
         <v>6155</v>
       </c>
       <c r="G803">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H803" t="s">
         <v>101</v>
@@ -31279,7 +31285,7 @@
         <v>129</v>
       </c>
       <c r="G804">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H804" t="s">
         <v>101</v>
@@ -31317,7 +31323,7 @@
         <v>3030</v>
       </c>
       <c r="G805">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H805" t="s">
         <v>101</v>
@@ -31355,7 +31361,7 @@
         <v>3331</v>
       </c>
       <c r="G806">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H806" t="s">
         <v>101</v>
@@ -31393,7 +31399,7 @@
         <v>23592</v>
       </c>
       <c r="G807">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H807" t="s">
         <v>101</v>
@@ -31431,7 +31437,7 @@
         <v>30741</v>
       </c>
       <c r="G808">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H808" t="s">
         <v>101</v>
@@ -31469,7 +31475,7 @@
         <v>1068</v>
       </c>
       <c r="G809">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H809" t="s">
         <v>101</v>
@@ -31507,7 +31513,7 @@
         <v>4365</v>
       </c>
       <c r="G810">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H810" t="s">
         <v>101</v>
@@ -31545,7 +31551,7 @@
         <v>5572</v>
       </c>
       <c r="G811">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H811" t="s">
         <v>101</v>
@@ -31583,7 +31589,7 @@
         <v>11092</v>
       </c>
       <c r="G812">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H812" t="s">
         <v>101</v>
@@ -31621,7 +31627,7 @@
         <v>14755</v>
       </c>
       <c r="G813">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H813" t="s">
         <v>101</v>
@@ -31659,7 +31665,7 @@
         <v>925</v>
       </c>
       <c r="G814">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H814" t="s">
         <v>101</v>
@@ -31697,7 +31703,7 @@
         <v>7873</v>
       </c>
       <c r="G815">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H815" t="s">
         <v>101</v>
@@ -31735,7 +31741,7 @@
         <v>8827</v>
       </c>
       <c r="G816">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H816" t="s">
         <v>101</v>
@@ -31773,7 +31779,7 @@
         <v>3346</v>
       </c>
       <c r="G817">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H817" t="s">
         <v>101</v>
@@ -31811,7 +31817,7 @@
         <v>3394</v>
       </c>
       <c r="G818">
-        <v>271750</v>
+        <v>278750</v>
       </c>
       <c r="H818" t="s">
         <v>101</v>
@@ -31849,7 +31855,7 @@
         <v>39481</v>
       </c>
       <c r="G819">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H819" t="s">
         <v>103</v>
@@ -31887,7 +31893,7 @@
         <v>41440</v>
       </c>
       <c r="G820">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H820" t="s">
         <v>103</v>
@@ -31925,7 +31931,7 @@
         <v>6738</v>
       </c>
       <c r="G821">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H821" t="s">
         <v>103</v>
@@ -31963,7 +31969,7 @@
         <v>7698</v>
       </c>
       <c r="G822">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H822" t="s">
         <v>103</v>
@@ -32001,7 +32007,7 @@
         <v>15743</v>
       </c>
       <c r="G823">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H823" t="s">
         <v>103</v>
@@ -32039,7 +32045,7 @@
         <v>17805</v>
       </c>
       <c r="G824">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H824" t="s">
         <v>103</v>
@@ -32077,7 +32083,7 @@
         <v>9116</v>
       </c>
       <c r="G825">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H825" t="s">
         <v>103</v>
@@ -32115,7 +32121,7 @@
         <v>9129</v>
       </c>
       <c r="G826">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H826" t="s">
         <v>103</v>
@@ -32153,7 +32159,7 @@
         <v>4956</v>
       </c>
       <c r="G827">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H827" t="s">
         <v>103</v>
@@ -32191,7 +32197,7 @@
         <v>4662</v>
       </c>
       <c r="G828">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H828" t="s">
         <v>103</v>
@@ -32229,7 +32235,7 @@
         <v>42488</v>
       </c>
       <c r="G829">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H829" t="s">
         <v>103</v>
@@ -32267,7 +32273,7 @@
         <v>43392</v>
       </c>
       <c r="G830">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H830" t="s">
         <v>103</v>
@@ -32305,7 +32311,7 @@
         <v>7193</v>
       </c>
       <c r="G831">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H831" t="s">
         <v>103</v>
@@ -32343,7 +32349,7 @@
         <v>8638</v>
       </c>
       <c r="G832">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H832" t="s">
         <v>103</v>
@@ -32381,7 +32387,7 @@
         <v>17203</v>
       </c>
       <c r="G833">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H833" t="s">
         <v>103</v>
@@ -32419,7 +32425,7 @@
         <v>16492</v>
       </c>
       <c r="G834">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H834" t="s">
         <v>103</v>
@@ -32457,7 +32463,7 @@
         <v>10168</v>
       </c>
       <c r="G835">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H835" t="s">
         <v>103</v>
@@ -32495,7 +32501,7 @@
         <v>11219</v>
       </c>
       <c r="G836">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H836" t="s">
         <v>103</v>
@@ -32533,7 +32539,7 @@
         <v>5101</v>
       </c>
       <c r="G837">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H837" t="s">
         <v>103</v>
@@ -32571,7 +32577,7 @@
         <v>5089</v>
       </c>
       <c r="G838">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H838" t="s">
         <v>103</v>
@@ -32609,7 +32615,7 @@
         <v>39975</v>
       </c>
       <c r="G839">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H839" t="s">
         <v>103</v>
@@ -32647,7 +32653,7 @@
         <v>6423</v>
       </c>
       <c r="G840">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H840" t="s">
         <v>103</v>
@@ -32685,7 +32691,7 @@
         <v>7770</v>
       </c>
       <c r="G841">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H841" t="s">
         <v>103</v>
@@ -32723,7 +32729,7 @@
         <v>16801</v>
       </c>
       <c r="G842">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H842" t="s">
         <v>103</v>
@@ -32761,7 +32767,7 @@
         <v>18225</v>
       </c>
       <c r="G843">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H843" t="s">
         <v>103</v>
@@ -32799,7 +32805,7 @@
         <v>10243</v>
       </c>
       <c r="G844">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H844" t="s">
         <v>103</v>
@@ -32837,7 +32843,7 @@
         <v>5028</v>
       </c>
       <c r="G845">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H845" t="s">
         <v>103</v>
@@ -32875,7 +32881,7 @@
         <v>5003</v>
       </c>
       <c r="G846">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H846" t="s">
         <v>103</v>
@@ -32913,7 +32919,7 @@
         <v>47663</v>
       </c>
       <c r="G847">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H847" t="s">
         <v>103</v>
@@ -32951,7 +32957,7 @@
         <v>48683</v>
       </c>
       <c r="G848">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H848" t="s">
         <v>103</v>
@@ -32989,7 +32995,7 @@
         <v>7926</v>
       </c>
       <c r="G849">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H849" t="s">
         <v>103</v>
@@ -33027,7 +33033,7 @@
         <v>8329</v>
       </c>
       <c r="G850">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H850" t="s">
         <v>103</v>
@@ -33065,7 +33071,7 @@
         <v>18110</v>
       </c>
       <c r="G851">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H851" t="s">
         <v>103</v>
@@ -33103,7 +33109,7 @@
         <v>21609</v>
       </c>
       <c r="G852">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H852" t="s">
         <v>103</v>
@@ -33141,7 +33147,7 @@
         <v>10529</v>
       </c>
       <c r="G853">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H853" t="s">
         <v>103</v>
@@ -33179,7 +33185,7 @@
         <v>11213</v>
       </c>
       <c r="G854">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H854" t="s">
         <v>103</v>
@@ -33217,7 +33223,7 @@
         <v>5194</v>
       </c>
       <c r="G855">
-        <v>131450</v>
+        <v>263080</v>
       </c>
       <c r="H855" t="s">
         <v>103</v>
@@ -33255,7 +33261,7 @@
         <v>23999</v>
       </c>
       <c r="G856">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H856" t="s">
         <v>107</v>
@@ -33293,7 +33299,7 @@
         <v>1581</v>
       </c>
       <c r="G857">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H857" t="s">
         <v>107</v>
@@ -33331,7 +33337,7 @@
         <v>4572</v>
       </c>
       <c r="G858">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H858" t="s">
         <v>107</v>
@@ -33369,7 +33375,7 @@
         <v>10997</v>
       </c>
       <c r="G859">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H859" t="s">
         <v>107</v>
@@ -33407,7 +33413,7 @@
         <v>755</v>
       </c>
       <c r="G860">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H860" t="s">
         <v>107</v>
@@ -33445,7 +33451,7 @@
         <v>6860</v>
       </c>
       <c r="G861">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H861" t="s">
         <v>107</v>
@@ -33483,7 +33489,7 @@
         <v>3841</v>
       </c>
       <c r="G862">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H862" t="s">
         <v>107</v>
@@ -33521,7 +33527,7 @@
         <v>23637</v>
       </c>
       <c r="G863">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H863" t="s">
         <v>107</v>
@@ -33559,7 +33565,7 @@
         <v>1920</v>
       </c>
       <c r="G864">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H864" t="s">
         <v>107</v>
@@ -33597,7 +33603,7 @@
         <v>3784</v>
       </c>
       <c r="G865">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H865" t="s">
         <v>107</v>
@@ -33635,7 +33641,7 @@
         <v>269</v>
       </c>
       <c r="G866">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H866" t="s">
         <v>107</v>
@@ -33673,7 +33679,7 @@
         <v>10710</v>
       </c>
       <c r="G867">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H867" t="s">
         <v>107</v>
@@ -33711,7 +33717,7 @@
         <v>5954</v>
       </c>
       <c r="G868">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H868" t="s">
         <v>107</v>
@@ -33749,7 +33755,7 @@
         <v>3097</v>
       </c>
       <c r="G869">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H869" t="s">
         <v>107</v>
@@ -33787,7 +33793,7 @@
         <v>30659</v>
       </c>
       <c r="G870">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H870" t="s">
         <v>107</v>
@@ -33825,7 +33831,7 @@
         <v>5121</v>
       </c>
       <c r="G871">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H871" t="s">
         <v>107</v>
@@ -33863,7 +33869,7 @@
         <v>12626</v>
       </c>
       <c r="G872">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H872" t="s">
         <v>107</v>
@@ -33901,7 +33907,7 @@
         <v>7342</v>
       </c>
       <c r="G873">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H873" t="s">
         <v>107</v>
@@ -33939,7 +33945,7 @@
         <v>3996</v>
       </c>
       <c r="G874">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H874" t="s">
         <v>107</v>
@@ -33977,7 +33983,7 @@
         <v>27858</v>
       </c>
       <c r="G875">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H875" t="s">
         <v>107</v>
@@ -34015,7 +34021,7 @@
         <v>4877</v>
       </c>
       <c r="G876">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H876" t="s">
         <v>107</v>
@@ -34053,7 +34059,7 @@
         <v>11432</v>
       </c>
       <c r="G877">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H877" t="s">
         <v>107</v>
@@ -34091,7 +34097,7 @@
         <v>983</v>
       </c>
       <c r="G878">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H878" t="s">
         <v>107</v>
@@ -34129,7 +34135,7 @@
         <v>6900</v>
       </c>
       <c r="G879">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H879" t="s">
         <v>107</v>
@@ -34167,7 +34173,7 @@
         <v>3997</v>
       </c>
       <c r="G880">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H880" t="s">
         <v>107</v>
@@ -34205,7 +34211,7 @@
         <v>24335</v>
       </c>
       <c r="G881">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H881" t="s">
         <v>107</v>
@@ -34243,7 +34249,7 @@
         <v>903</v>
       </c>
       <c r="G882">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H882" t="s">
         <v>107</v>
@@ -34281,7 +34287,7 @@
         <v>4749</v>
       </c>
       <c r="G883">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H883" t="s">
         <v>107</v>
@@ -34319,7 +34325,7 @@
         <v>10496</v>
       </c>
       <c r="G884">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H884" t="s">
         <v>107</v>
@@ -34357,7 +34363,7 @@
         <v>6122</v>
       </c>
       <c r="G885">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H885" t="s">
         <v>107</v>
@@ -34395,7 +34401,7 @@
         <v>2816</v>
       </c>
       <c r="G886">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H886" t="s">
         <v>107</v>
@@ -34433,7 +34439,7 @@
         <v>35355</v>
       </c>
       <c r="G887">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H887" t="s">
         <v>107</v>
@@ -34471,7 +34477,7 @@
         <v>2844</v>
       </c>
       <c r="G888">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H888" t="s">
         <v>107</v>
@@ -34509,7 +34515,7 @@
         <v>6367</v>
       </c>
       <c r="G889">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H889" t="s">
         <v>107</v>
@@ -34547,7 +34553,7 @@
         <v>14641</v>
       </c>
       <c r="G890">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H890" t="s">
         <v>107</v>
@@ -34585,7 +34591,7 @@
         <v>9202</v>
       </c>
       <c r="G891">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H891" t="s">
         <v>107</v>
@@ -34623,7 +34629,7 @@
         <v>4749</v>
       </c>
       <c r="G892">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H892" t="s">
         <v>107</v>
@@ -34661,7 +34667,7 @@
         <v>30065</v>
       </c>
       <c r="G893">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H893" t="s">
         <v>107</v>
@@ -34699,7 +34705,7 @@
         <v>1726</v>
       </c>
       <c r="G894">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H894" t="s">
         <v>107</v>
@@ -34737,7 +34743,7 @@
         <v>5347</v>
       </c>
       <c r="G895">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H895" t="s">
         <v>107</v>
@@ -34775,7 +34781,7 @@
         <v>12751</v>
       </c>
       <c r="G896">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H896" t="s">
         <v>107</v>
@@ -34813,7 +34819,7 @@
         <v>1648</v>
       </c>
       <c r="G897">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H897" t="s">
         <v>107</v>
@@ -34851,7 +34857,7 @@
         <v>8371</v>
       </c>
       <c r="G898">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H898" t="s">
         <v>107</v>
@@ -34889,7 +34895,7 @@
         <v>4354</v>
       </c>
       <c r="G899">
-        <v>174320</v>
+        <v>209200</v>
       </c>
       <c r="H899" t="s">
         <v>107</v>
@@ -34927,7 +34933,7 @@
         <v>25108</v>
       </c>
       <c r="G900">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H900" t="s">
         <v>111</v>
@@ -34965,7 +34971,7 @@
         <v>33933</v>
       </c>
       <c r="G901">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H901" t="s">
         <v>111</v>
@@ -35003,7 +35009,7 @@
         <v>1644</v>
       </c>
       <c r="G902">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H902" t="s">
         <v>111</v>
@@ -35041,7 +35047,7 @@
         <v>4627</v>
       </c>
       <c r="G903">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H903" t="s">
         <v>111</v>
@@ -35079,7 +35085,7 @@
         <v>5947</v>
       </c>
       <c r="G904">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H904" t="s">
         <v>111</v>
@@ -35117,7 +35123,7 @@
         <v>11302</v>
       </c>
       <c r="G905">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H905" t="s">
         <v>111</v>
@@ -35155,7 +35161,7 @@
         <v>15434</v>
       </c>
       <c r="G906">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H906" t="s">
         <v>111</v>
@@ -35193,7 +35199,7 @@
         <v>846</v>
       </c>
       <c r="G907">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H907" t="s">
         <v>111</v>
@@ -35231,7 +35237,7 @@
         <v>7837</v>
       </c>
       <c r="G908">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H908" t="s">
         <v>111</v>
@@ -35269,7 +35275,7 @@
         <v>8505</v>
       </c>
       <c r="G909">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H909" t="s">
         <v>111</v>
@@ -35307,7 +35313,7 @@
         <v>3112</v>
       </c>
       <c r="G910">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H910" t="s">
         <v>111</v>
@@ -35345,7 +35351,7 @@
         <v>3605</v>
       </c>
       <c r="G911">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H911" t="s">
         <v>111</v>
@@ -35383,7 +35389,7 @@
         <v>34263</v>
       </c>
       <c r="G912">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H912" t="s">
         <v>111</v>
@@ -35421,7 +35427,7 @@
         <v>35609</v>
       </c>
       <c r="G913">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H913" t="s">
         <v>111</v>
@@ -35459,7 +35465,7 @@
         <v>2811</v>
       </c>
       <c r="G914">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H914" t="s">
         <v>111</v>
@@ -35497,7 +35503,7 @@
         <v>6391</v>
       </c>
       <c r="G915">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H915" t="s">
         <v>111</v>
@@ -35535,7 +35541,7 @@
         <v>7363</v>
       </c>
       <c r="G916">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H916" t="s">
         <v>111</v>
@@ -35573,7 +35579,7 @@
         <v>15703</v>
       </c>
       <c r="G917">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H917" t="s">
         <v>111</v>
@@ -35611,7 +35617,7 @@
         <v>16798</v>
       </c>
       <c r="G918">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H918" t="s">
         <v>111</v>
@@ -35649,7 +35655,7 @@
         <v>1608</v>
       </c>
       <c r="G919">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H919" t="s">
         <v>111</v>
@@ -35687,7 +35693,7 @@
         <v>8904</v>
       </c>
       <c r="G920">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H920" t="s">
         <v>111</v>
@@ -35725,7 +35731,7 @@
         <v>9986</v>
       </c>
       <c r="G921">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H921" t="s">
         <v>111</v>
@@ -35763,7 +35769,7 @@
         <v>3755</v>
       </c>
       <c r="G922">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H922" t="s">
         <v>111</v>
@@ -35801,7 +35807,7 @@
         <v>4558</v>
       </c>
       <c r="G923">
-        <v>120000</v>
+        <v>154000</v>
       </c>
       <c r="H923" t="s">
         <v>111</v>
@@ -35839,7 +35845,7 @@
         <v>39356</v>
       </c>
       <c r="G924">
-        <v>168500</v>
+        <v>212050</v>
       </c>
       <c r="H924" t="s">
         <v>113</v>
@@ -35877,7 +35883,7 @@
         <v>44100</v>
       </c>
       <c r="G925">
-        <v>168500</v>
+        <v>212050</v>
       </c>
       <c r="H925" t="s">
         <v>113</v>
@@ -35915,7 +35921,7 @@
         <v>6856</v>
       </c>
       <c r="G926">
-        <v>168500</v>
+        <v>212050</v>
       </c>
       <c r="H926" t="s">
         <v>113</v>
@@ -35953,7 +35959,7 @@
         <v>7848</v>
       </c>
       <c r="G927">
-        <v>168500</v>
+        <v>212050</v>
       </c>
       <c r="H927" t="s">
         <v>113</v>
@@ -35991,7 +35997,7 @@
         <v>16297</v>
       </c>
       <c r="G928">
-        <v>168500</v>
+        <v>212050</v>
       </c>
       <c r="H928" t="s">
         <v>113</v>
@@ -36029,7 +36035,7 @@
         <v>19570</v>
       </c>
       <c r="G929">
-        <v>168500</v>
+        <v>212050</v>
       </c>
       <c r="H929" t="s">
         <v>113</v>
@@ -36067,7 +36073,7 @@
         <v>9014</v>
       </c>
       <c r="G930">
-        <v>168500</v>
+        <v>212050</v>
       </c>
       <c r="H930" t="s">
         <v>113</v>
@@ -36105,7 +36111,7 @@
         <v>11310</v>
       </c>
       <c r="G931">
-        <v>168500</v>
+        <v>212050</v>
       </c>
       <c r="H931" t="s">
         <v>113</v>
@@ -36143,7 +36149,7 @@
         <v>4278</v>
       </c>
       <c r="G932">
-        <v>168500</v>
+        <v>212050</v>
       </c>
       <c r="H932" t="s">
         <v>113</v>
@@ -36181,7 +36187,7 @@
         <v>4931</v>
       </c>
       <c r="G933">
-        <v>168500</v>
+        <v>212050</v>
       </c>
       <c r="H933" t="s">
         <v>113</v>
@@ -36219,10 +36225,10 @@
         <v>37788</v>
       </c>
       <c r="G934">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H934" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I934">
         <v>16.248502079516101</v>
@@ -36257,10 +36263,10 @@
         <v>42319</v>
       </c>
       <c r="G935">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H935" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I935">
         <v>16.248502079516101</v>
@@ -36295,10 +36301,10 @@
         <v>1738</v>
       </c>
       <c r="G936">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H936" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I936">
         <v>16.248502079516101</v>
@@ -36333,10 +36339,10 @@
         <v>6747</v>
       </c>
       <c r="G937">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H937" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I937">
         <v>16.248502079516101</v>
@@ -36371,10 +36377,10 @@
         <v>7471</v>
       </c>
       <c r="G938">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H938" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I938">
         <v>16.248502079516101</v>
@@ -36409,10 +36415,10 @@
         <v>15884</v>
       </c>
       <c r="G939">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H939" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I939">
         <v>16.248502079516101</v>
@@ -36447,10 +36453,10 @@
         <v>17427</v>
       </c>
       <c r="G940">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H940" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I940">
         <v>16.248502079516101</v>
@@ -36485,10 +36491,10 @@
         <v>1388</v>
       </c>
       <c r="G941">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H941" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I941">
         <v>16.248502079516101</v>
@@ -36523,10 +36529,10 @@
         <v>9414</v>
       </c>
       <c r="G942">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H942" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I942">
         <v>16.248502079516101</v>
@@ -36561,10 +36567,10 @@
         <v>6902</v>
       </c>
       <c r="G943">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H943" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I943">
         <v>16.248502079516101</v>
@@ -36599,10 +36605,10 @@
         <v>3896</v>
       </c>
       <c r="G944">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H944" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I944">
         <v>16.248502079516101</v>
@@ -36637,10 +36643,10 @@
         <v>3727</v>
       </c>
       <c r="G945">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H945" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I945">
         <v>16.248502079516101</v>
@@ -36675,10 +36681,10 @@
         <v>34282</v>
       </c>
       <c r="G946">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H946" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I946">
         <v>16.248502079516101</v>
@@ -36713,10 +36719,10 @@
         <v>38721</v>
       </c>
       <c r="G947">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H947" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I947">
         <v>16.248502079516101</v>
@@ -36751,10 +36757,10 @@
         <v>1090</v>
       </c>
       <c r="G948">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H948" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I948">
         <v>16.248502079516101</v>
@@ -36789,10 +36795,10 @@
         <v>5934</v>
       </c>
       <c r="G949">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H949" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I949">
         <v>16.248502079516101</v>
@@ -36827,10 +36833,10 @@
         <v>6273</v>
       </c>
       <c r="G950">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H950" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I950">
         <v>16.248502079516101</v>
@@ -36865,10 +36871,10 @@
         <v>230</v>
       </c>
       <c r="G951">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H951" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I951">
         <v>16.248502079516101</v>
@@ -36903,10 +36909,10 @@
         <v>14422</v>
       </c>
       <c r="G952">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H952" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I952">
         <v>16.248502079516101</v>
@@ -36941,10 +36947,10 @@
         <v>15948</v>
       </c>
       <c r="G953">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H953" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I953">
         <v>16.248502079516101</v>
@@ -36979,10 +36985,10 @@
         <v>506</v>
       </c>
       <c r="G954">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H954" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I954">
         <v>16.248502079516101</v>
@@ -37017,10 +37023,10 @@
         <v>9130</v>
       </c>
       <c r="G955">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H955" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I955">
         <v>16.248502079516101</v>
@@ -37055,10 +37061,10 @@
         <v>8823</v>
       </c>
       <c r="G956">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H956" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I956">
         <v>16.248502079516101</v>
@@ -37093,10 +37099,10 @@
         <v>3696</v>
       </c>
       <c r="G957">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H957" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I957">
         <v>16.248502079516101</v>
@@ -37131,10 +37137,10 @@
         <v>2997</v>
       </c>
       <c r="G958">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H958" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I958">
         <v>16.248502079516101</v>
@@ -37169,10 +37175,10 @@
         <v>39100</v>
       </c>
       <c r="G959">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H959" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I959">
         <v>16.248502079516101</v>
@@ -37207,10 +37213,10 @@
         <v>41131</v>
       </c>
       <c r="G960">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H960" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I960">
         <v>16.248502079516101</v>
@@ -37245,10 +37251,10 @@
         <v>1431</v>
       </c>
       <c r="G961">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H961" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I961">
         <v>16.248502079516101</v>
@@ -37283,10 +37289,10 @@
         <v>6986</v>
       </c>
       <c r="G962">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H962" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I962">
         <v>16.248502079516101</v>
@@ -37321,10 +37327,10 @@
         <v>7666</v>
       </c>
       <c r="G963">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H963" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I963">
         <v>16.248502079516101</v>
@@ -37359,10 +37365,10 @@
         <v>16256</v>
       </c>
       <c r="G964">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H964" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I964">
         <v>16.248502079516101</v>
@@ -37397,10 +37403,10 @@
         <v>18537</v>
       </c>
       <c r="G965">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H965" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I965">
         <v>16.248502079516101</v>
@@ -37435,10 +37441,10 @@
         <v>10071</v>
       </c>
       <c r="G966">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H966" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I966">
         <v>16.248502079516101</v>
@@ -37473,10 +37479,10 @@
         <v>11471</v>
       </c>
       <c r="G967">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H967" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I967">
         <v>16.248502079516101</v>
@@ -37511,10 +37517,10 @@
         <v>4460</v>
       </c>
       <c r="G968">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H968" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I968">
         <v>16.248502079516101</v>
@@ -37549,10 +37555,10 @@
         <v>4854</v>
       </c>
       <c r="G969">
-        <v>183775</v>
+        <v>272000</v>
       </c>
       <c r="H969" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I969">
         <v>16.248502079516101</v>
@@ -37569,7 +37575,7 @@
     </row>
     <row r="970" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A970" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B970" t="s">
         <v>11</v>
@@ -37587,10 +37593,10 @@
         <v>32396</v>
       </c>
       <c r="G970">
-        <v>163810</v>
+        <v>243120</v>
       </c>
       <c r="H970" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I970">
         <v>20.718174950000002</v>
@@ -37607,7 +37613,7 @@
     </row>
     <row r="971" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A971" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B971" t="s">
         <v>11</v>
@@ -37625,10 +37631,10 @@
         <v>38839</v>
       </c>
       <c r="G971">
-        <v>163810</v>
+        <v>243120</v>
       </c>
       <c r="H971" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I971">
         <v>20.718174950000002</v>
@@ -37645,7 +37651,7 @@
     </row>
     <row r="972" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A972" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B972" t="s">
         <v>11</v>
@@ -37663,10 +37669,10 @@
         <v>2211</v>
       </c>
       <c r="G972">
-        <v>163810</v>
+        <v>243120</v>
       </c>
       <c r="H972" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I972">
         <v>20.718174950000002</v>
@@ -37683,7 +37689,7 @@
     </row>
     <row r="973" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A973" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B973" t="s">
         <v>11</v>
@@ -37701,10 +37707,10 @@
         <v>2221</v>
       </c>
       <c r="G973">
-        <v>163810</v>
+        <v>243120</v>
       </c>
       <c r="H973" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I973">
         <v>20.718174950000002</v>
@@ -37721,7 +37727,7 @@
     </row>
     <row r="974" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A974" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B974" t="s">
         <v>11</v>
@@ -37739,10 +37745,10 @@
         <v>5983</v>
       </c>
       <c r="G974">
-        <v>163810</v>
+        <v>243120</v>
       </c>
       <c r="H974" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I974">
         <v>20.718174950000002</v>
@@ -37759,7 +37765,7 @@
     </row>
     <row r="975" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A975" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B975" t="s">
         <v>11</v>
@@ -37777,10 +37783,10 @@
         <v>7291</v>
       </c>
       <c r="G975">
-        <v>163810</v>
+        <v>243120</v>
       </c>
       <c r="H975" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I975">
         <v>20.718174950000002</v>
@@ -37797,7 +37803,7 @@
     </row>
     <row r="976" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A976" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B976" t="s">
         <v>11</v>
@@ -37815,10 +37821,10 @@
         <v>15207</v>
       </c>
       <c r="G976">
-        <v>163810</v>
+        <v>243120</v>
       </c>
       <c r="H976" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I976">
         <v>20.718174950000002</v>
@@ -37835,7 +37841,7 @@
     </row>
     <row r="977" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A977" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B977" t="s">
         <v>11</v>
@@ -37853,10 +37859,10 @@
         <v>18963</v>
       </c>
       <c r="G977">
-        <v>163810</v>
+        <v>243120</v>
       </c>
       <c r="H977" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I977">
         <v>20.718174950000002</v>
@@ -37873,7 +37879,7 @@
     </row>
     <row r="978" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A978" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B978" t="s">
         <v>11</v>
@@ -37891,10 +37897,10 @@
         <v>1077</v>
       </c>
       <c r="G978">
-        <v>163810</v>
+        <v>243120</v>
       </c>
       <c r="H978" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I978">
         <v>20.718174950000002</v>
@@ -37911,7 +37917,7 @@
     </row>
     <row r="979" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A979" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B979" t="s">
         <v>11</v>
@@ -37929,10 +37935,10 @@
         <v>9163</v>
       </c>
       <c r="G979">
-        <v>163810</v>
+        <v>243120</v>
       </c>
       <c r="H979" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I979">
         <v>20.718174950000002</v>
@@ -37949,7 +37955,7 @@
     </row>
     <row r="980" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A980" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B980" t="s">
         <v>11</v>
@@ -37967,10 +37973,10 @@
         <v>11061</v>
       </c>
       <c r="G980">
-        <v>163810</v>
+        <v>243120</v>
       </c>
       <c r="H980" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I980">
         <v>20.718174950000002</v>
@@ -37987,7 +37993,7 @@
     </row>
     <row r="981" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A981" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B981" t="s">
         <v>11</v>
@@ -38005,10 +38011,10 @@
         <v>4629</v>
       </c>
       <c r="G981">
-        <v>163810</v>
+        <v>243120</v>
       </c>
       <c r="H981" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I981">
         <v>20.718174950000002</v>
@@ -38025,7 +38031,7 @@
     </row>
     <row r="982" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A982" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B982" t="s">
         <v>11</v>
@@ -38043,10 +38049,10 @@
         <v>4099</v>
       </c>
       <c r="G982">
-        <v>163810</v>
+        <v>243120</v>
       </c>
       <c r="H982" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I982">
         <v>20.718174950000002</v>
